--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="9"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1270">
   <si>
     <t>Мисъл</t>
   </si>
@@ -6127,6 +6127,271 @@
   </si>
   <si>
     <t>Копуване на имоти</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Това не е обвинение. Това е </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>стандарт</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Просто приех как се развиха нещата между нас и реших да продължа напред"</t>
+  </si>
+  <si>
+    <t>"Просто видях как се промени отношението към мен и реших да продължа напред"</t>
+  </si>
+  <si>
+    <t>"В един момент усетих, че давам повече енергия, отколкото получавам. Затова реших да се отдръпна."</t>
+  </si>
+  <si>
+    <t>"Мисля, че всеки от нас тръгна по своя път. Аз просто се опитвам да живея по-спокойно"</t>
+  </si>
+  <si>
+    <t>тя контролира дистанцията</t>
+  </si>
+  <si>
+    <t>ти инвестираш повече</t>
+  </si>
+  <si>
+    <t>ти чакаш време от нея</t>
+  </si>
+  <si>
+    <t>тя се появява, когато ѝ е удобно</t>
+  </si>
+  <si>
+    <t>Възможни отговори на "Променил си се"</t>
+  </si>
+  <si>
+    <t>„Ти ме игнорираше…“</t>
+  </si>
+  <si>
+    <t>„Аз се борих 10 години…</t>
+  </si>
+  <si>
+    <t>„Ти не ме оценяваше…“</t>
+  </si>
+  <si>
+    <t>Ключът е да не го обясняваш като обвинение към нея, а като естествена промяна в теб.</t>
+  </si>
+  <si>
+    <t>Тези неща може да са верни, но ги превръщат в спор</t>
+  </si>
+  <si>
+    <t>Ти не я наказваш.</t>
+  </si>
+  <si>
+    <t>Ти не играеш игра</t>
+  </si>
+  <si>
+    <t>Ти просто вече не инвестираш там, където няма взаимност</t>
+  </si>
+  <si>
+    <t>Ако приемеш същата динамика („близки, но не сериозно“), моделът автоматично ще се върне:</t>
+  </si>
+  <si>
+    <t>Ако някога разговорът стигне до връщане на отношенията, можеш спокойно да кажеш нещо такова:</t>
+  </si>
+  <si>
+    <t>„Не мисля, че това би било добро за мен. Ако съм с някого, искам връзката да е ясна и взаимна.“</t>
+  </si>
+  <si>
+    <t>Нейното отношение:</t>
+  </si>
+  <si>
+    <t>картички за празници</t>
+  </si>
+  <si>
+    <t>обаждане</t>
+  </si>
+  <si>
+    <t>въпроси за живота ти</t>
+  </si>
+  <si>
+    <t>снимки от пътуване</t>
+  </si>
+  <si>
+    <t>закачка „не пита къде е“</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Това са </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>контактни сонди</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Не са покана за връзка.</t>
+    </r>
+  </si>
+  <si>
+    <t>Тя проверява:</t>
+  </si>
+  <si>
+    <t>дали още си там</t>
+  </si>
+  <si>
+    <t>дали още реагираш</t>
+  </si>
+  <si>
+    <t>дали още има влияние върху теб</t>
+  </si>
+  <si>
+    <t>Жените уважават много повече мъж, който може да се отдръпне, отколкото мъж, който остава на разположение без край</t>
+  </si>
+  <si>
+    <t>дали още има интерес от твоя страна</t>
+  </si>
+  <si>
+    <t>дали още може да предизвика емоция</t>
+  </si>
+  <si>
+    <t>дали връзката между вас не е напълно изчезнала</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Но това </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не означава непременно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, че тя иска да се върне във връзката</t>
+    </r>
+  </si>
+  <si>
+    <t>Поведението и:</t>
+  </si>
+  <si>
+    <t>изпраща снимка → но не пита нищо за теб</t>
+  </si>
+  <si>
+    <t>започва разговор → но бърза да го приключи</t>
+  </si>
+  <si>
+    <t>появява се → после пак изчезва</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Този модел по-скоро прилича на </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>поддържане на контакт</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, а </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> на реално приближаване.</t>
+    </r>
+  </si>
+  <si>
+    <t>Не я обвиняваш:</t>
+  </si>
+  <si>
+    <t>Твоето отношение:</t>
+  </si>
+  <si>
+    <t>Ти:</t>
+  </si>
+  <si>
+    <t>отговаряш спокойно</t>
+  </si>
+  <si>
+    <t>не преследваш</t>
+  </si>
+  <si>
+    <t>не се опитваш да впечатляваш</t>
+  </si>
+  <si>
+    <t>не се обясняваш</t>
   </si>
 </sst>
 </file>
@@ -6539,7 +6804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6643,7 +6908,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -6658,6 +6922,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12793,7 +13059,7 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="86" t="s">
         <v>1207</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -12808,10 +13074,10 @@
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="88">
+      <c r="B7" s="87">
         <v>300000</v>
       </c>
-      <c r="D7" s="89">
+      <c r="D7" s="88">
         <v>300000</v>
       </c>
       <c r="E7" s="7"/>
@@ -12823,7 +13089,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="90"/>
+      <c r="B8" s="89"/>
       <c r="D8" s="3"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -12834,7 +13100,7 @@
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="90"/>
+      <c r="B9" s="89"/>
       <c r="D9" s="3"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -12845,7 +13111,7 @@
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="89" t="s">
         <v>1208</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -12860,7 +13126,7 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="89" t="s">
         <v>1210</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -12875,7 +13141,7 @@
       <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="90" t="s">
         <v>1211</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -12896,7 +13162,7 @@
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="92"/>
+      <c r="G13" s="91"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
@@ -12909,7 +13175,7 @@
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="92"/>
+      <c r="G14" s="91"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
@@ -12922,7 +13188,7 @@
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="92"/>
+      <c r="G15" s="91"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -12935,7 +13201,7 @@
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="92"/>
+      <c r="G16" s="91"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -12948,7 +13214,7 @@
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="92"/>
+      <c r="G17" s="91"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -12961,7 +13227,7 @@
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="92"/>
+      <c r="G18" s="91"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -12974,7 +13240,7 @@
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="92"/>
+      <c r="G19" s="91"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -12987,7 +13253,7 @@
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
-      <c r="G20" s="93"/>
+      <c r="G20" s="92"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -17611,7 +17877,7 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="84" t="s">
         <v>1201</v>
       </c>
       <c r="F6" t="s">
@@ -17635,7 +17901,7 @@
       <c r="B14" s="75"/>
       <c r="C14" s="75"/>
       <c r="D14" s="75"/>
-      <c r="E14" s="82"/>
+      <c r="E14" s="81"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
     </row>
@@ -17643,7 +17909,7 @@
       <c r="B15" s="75"/>
       <c r="C15" s="75"/>
       <c r="D15" s="75"/>
-      <c r="E15" s="83"/>
+      <c r="E15" s="82"/>
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
     </row>
@@ -17651,7 +17917,7 @@
       <c r="B16" s="75"/>
       <c r="C16" s="75"/>
       <c r="D16" s="75"/>
-      <c r="E16" s="83"/>
+      <c r="E16" s="82"/>
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
     </row>
@@ -17659,7 +17925,7 @@
       <c r="B17" s="75"/>
       <c r="C17" s="75"/>
       <c r="D17" s="75"/>
-      <c r="E17" s="83"/>
+      <c r="E17" s="82"/>
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
     </row>
@@ -17667,7 +17933,7 @@
       <c r="B18" s="75"/>
       <c r="C18" s="76"/>
       <c r="D18" s="75"/>
-      <c r="E18" s="83"/>
+      <c r="E18" s="82"/>
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
     </row>
@@ -17675,7 +17941,7 @@
       <c r="B19" s="75"/>
       <c r="C19" s="76"/>
       <c r="D19" s="75"/>
-      <c r="E19" s="83"/>
+      <c r="E19" s="82"/>
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
     </row>
@@ -17683,7 +17949,7 @@
       <c r="B20" s="75"/>
       <c r="C20" s="75"/>
       <c r="D20" s="75"/>
-      <c r="E20" s="84"/>
+      <c r="E20" s="83"/>
       <c r="F20" s="10"/>
       <c r="G20" s="11"/>
     </row>
@@ -17691,7 +17957,7 @@
       <c r="B21" s="75"/>
       <c r="C21" s="75"/>
       <c r="D21" s="75"/>
-      <c r="E21" s="86"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
     </row>
@@ -17699,7 +17965,7 @@
       <c r="B22" s="75"/>
       <c r="C22" s="75"/>
       <c r="D22" s="75"/>
-      <c r="E22" s="86"/>
+      <c r="E22" s="85"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
     </row>
@@ -17707,7 +17973,7 @@
       <c r="B23" s="75"/>
       <c r="C23" s="75"/>
       <c r="D23" s="75"/>
-      <c r="E23" s="86"/>
+      <c r="E23" s="85"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
     </row>
@@ -17715,7 +17981,7 @@
       <c r="B24" s="75"/>
       <c r="C24" s="75"/>
       <c r="D24" s="75"/>
-      <c r="E24" s="86"/>
+      <c r="E24" s="85"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
     </row>
@@ -17723,7 +17989,7 @@
       <c r="B25" s="75"/>
       <c r="C25" s="75"/>
       <c r="D25" s="75"/>
-      <c r="E25" s="86"/>
+      <c r="E25" s="85"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
     </row>
@@ -17731,7 +17997,7 @@
       <c r="B26" s="75"/>
       <c r="C26" s="75"/>
       <c r="D26" s="75"/>
-      <c r="E26" s="86"/>
+      <c r="E26" s="85"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
     </row>
@@ -18332,11 +18598,8 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="16" t="s">
@@ -18353,6 +18616,7 @@
       <c r="E3" s="16" t="s">
         <v>1107</v>
       </c>
+      <c r="F3" s="16"/>
       <c r="H3" s="16" t="s">
         <v>512</v>
       </c>
@@ -18364,7 +18628,6 @@
       <c r="B4" t="s">
         <v>1110</v>
       </c>
-      <c r="F4" s="81"/>
       <c r="H4" t="s">
         <v>1111</v>
       </c>
@@ -18394,11 +18657,273 @@
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="F8" s="81"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
         <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="16" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="16"/>
+      <c r="B101" s="94" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="16"/>
+      <c r="B102" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="16"/>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>1</v>
+      </c>
+      <c r="B104" s="93" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107">
+        <v>2</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>3</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="16" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="16"/>
+      <c r="B111" s="16" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F111" s="16" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="16"/>
+      <c r="C112" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="16"/>
+      <c r="C113" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="16"/>
+      <c r="C114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="16"/>
+      <c r="C115" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="16"/>
+      <c r="C116" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="16"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="16"/>
+      <c r="C118" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="16"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="16"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="16" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="16"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="B123" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="B124" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="B125" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="B126" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="B128" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="C129" s="22" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="16" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="B132" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="B133" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="B134" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="B135" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="B136" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="B138" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="B140" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="C141" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G141" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="C142" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G142" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="C143" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G143" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3">
+      <c r="B145" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3">
+      <c r="B147" s="22" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3">
+      <c r="B149" s="16" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3">
+      <c r="C150" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3">
+      <c r="C151" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3">
+      <c r="C152" s="22" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3">
+      <c r="C154" t="s">
+        <v>1262</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1277">
   <si>
     <t>Мисъл</t>
   </si>
@@ -3509,9 +3509,6 @@
     <t>3. Може да бъде подготвка на настроението за тренировка(хубава музика)</t>
   </si>
   <si>
-    <t>Кога то дойде времето зьа действието описано в организацията - да се направи</t>
-  </si>
-  <si>
     <t>Да достигна до най-върховната си версия</t>
   </si>
   <si>
@@ -3848,15 +3845,9 @@
     <t>Голяма фирма</t>
   </si>
   <si>
-    <t>Богати клиенти</t>
-  </si>
-  <si>
     <t>Подходящи хора</t>
   </si>
   <si>
-    <t>Вид източник</t>
-  </si>
-  <si>
     <t>Пламен</t>
   </si>
   <si>
@@ -5859,9 +5850,6 @@
     <t>Като съм благодарен за това което имам</t>
   </si>
   <si>
-    <t>Като правя всеки ден нещо което е трудно, неприят н оза мен</t>
-  </si>
-  <si>
     <t>Цели личностни</t>
   </si>
   <si>
@@ -6392,18 +6380,59 @@
   </si>
   <si>
     <t>не се обясняваш</t>
+  </si>
+  <si>
+    <t>Като правя всеки ден нещо което е трудно, неприятно за мен</t>
+  </si>
+  <si>
+    <t>Кога то дойде времето за действието описано в организацията - да се направи</t>
+  </si>
+  <si>
+    <t>Какво ще е нещото което ще се търси след 5 години?</t>
+  </si>
+  <si>
+    <t>програмисти</t>
+  </si>
+  <si>
+    <t>не</t>
+  </si>
+  <si>
+    <t>електротехници</t>
+  </si>
+  <si>
+    <t>да</t>
+  </si>
+  <si>
+    <t>пто</t>
+  </si>
+  <si>
+    <t>Идея</t>
+  </si>
+  <si>
+    <t>Ел. Услуги на богати клиенти</t>
+  </si>
+  <si>
+    <t>Възможност за изтегляне на добър кредит</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6821,93 +6850,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -6922,8 +6951,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10404,7 +10433,7 @@
       <c r="G11" s="12"/>
       <c r="H11" s="7"/>
       <c r="I11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -10422,13 +10451,13 @@
         <v>177</v>
       </c>
       <c r="I12" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="J12" s="24" t="s">
         <v>522</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="K12" s="24" t="s">
         <v>523</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>524</v>
       </c>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
@@ -10449,7 +10478,7 @@
     <row r="14" spans="1:14">
       <c r="A14" s="3"/>
       <c r="C14" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -10516,7 +10545,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="C19" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
@@ -10528,7 +10557,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="C20" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D20" t="s">
         <v>240</v>
@@ -10542,7 +10571,7 @@
         <v>44</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -10557,7 +10586,7 @@
         <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -10567,7 +10596,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="8"/>
       <c r="K22" s="29" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -10579,7 +10608,7 @@
         <v>239</v>
       </c>
       <c r="K23" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -10593,7 +10622,7 @@
     <row r="25" spans="1:15">
       <c r="C25" s="44"/>
       <c r="D25" s="45" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E25" s="46"/>
     </row>
@@ -10679,7 +10708,7 @@
     </row>
     <row r="34" spans="2:15">
       <c r="B34" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="7"/>
@@ -10727,7 +10756,7 @@
         <v>203</v>
       </c>
       <c r="H39" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -10735,7 +10764,7 @@
         <v>204</v>
       </c>
       <c r="H40" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -10743,7 +10772,7 @@
         <v>205</v>
       </c>
       <c r="H41" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -10751,7 +10780,7 @@
         <v>207</v>
       </c>
       <c r="H42" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -10786,7 +10815,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="D49" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -12950,87 +12979,87 @@
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="16" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="552" spans="1:6">
       <c r="B552" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="553" spans="1:6">
       <c r="B553" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="555" spans="1:6">
       <c r="B555" s="16" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="556" spans="1:6">
       <c r="C556" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="557" spans="1:6">
       <c r="C557" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="558" spans="1:6">
       <c r="C558" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="560" spans="1:6">
       <c r="B560" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="562" spans="2:3">
       <c r="B562" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="564" spans="2:3">
       <c r="B564" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="565" spans="2:3">
       <c r="C565" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="566" spans="2:3">
       <c r="C566" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="567" spans="2:3">
       <c r="C567" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="569" spans="2:3">
       <c r="B569" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="571" spans="2:3">
       <c r="B571" s="16" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="572" spans="2:3">
       <c r="C572" s="58" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="573" spans="2:3">
       <c r="C573" s="58" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -13047,23 +13076,23 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D4" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="86" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -13112,10 +13141,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="B10" s="89" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -13127,10 +13156,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="89" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -13142,10 +13171,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="90" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -13158,7 +13187,7 @@
     <row r="13" spans="1:11">
       <c r="C13" s="62"/>
       <c r="D13" s="3" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -13171,7 +13200,7 @@
     <row r="14" spans="1:11">
       <c r="C14" s="62"/>
       <c r="D14" s="3" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -13184,7 +13213,7 @@
     <row r="15" spans="1:11">
       <c r="C15" s="62"/>
       <c r="D15" s="3" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -13197,7 +13226,7 @@
     <row r="16" spans="1:11">
       <c r="C16" s="62"/>
       <c r="D16" s="3" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -13210,7 +13239,7 @@
     <row r="17" spans="3:11">
       <c r="C17" s="62"/>
       <c r="D17" s="3" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -13223,7 +13252,7 @@
     <row r="18" spans="3:11">
       <c r="C18" s="62"/>
       <c r="D18" s="3" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -13236,7 +13265,7 @@
     <row r="19" spans="3:11">
       <c r="C19" s="62"/>
       <c r="D19" s="3" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -13249,7 +13278,7 @@
     <row r="20" spans="3:11">
       <c r="C20" s="62"/>
       <c r="D20" s="4" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -13265,7 +13294,7 @@
     </row>
     <row r="22" spans="3:11">
       <c r="C22" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="G22" s="63"/>
     </row>
@@ -13284,7 +13313,7 @@
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" s="16" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -13406,12 +13435,12 @@
     </row>
     <row r="24" spans="1:12">
       <c r="B24" t="s">
-        <v>502</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -13441,11 +13470,11 @@
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
       <c r="F29" s="43" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="48" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="8"/>
@@ -13454,7 +13483,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="B30" s="42" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
@@ -13471,22 +13500,22 @@
     </row>
     <row r="31" spans="1:12">
       <c r="B31" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>529</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="3"/>
@@ -13494,19 +13523,19 @@
     </row>
     <row r="32" spans="1:12">
       <c r="B32" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="8"/>
       <c r="E32" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>517</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="8"/>
@@ -13515,7 +13544,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="B33" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="8"/>
@@ -13525,7 +13554,7 @@
       <c r="F33" s="7"/>
       <c r="G33" s="8"/>
       <c r="H33" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="8"/>
@@ -13534,19 +13563,19 @@
     </row>
     <row r="34" spans="1:12">
       <c r="B34" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
       <c r="E34" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="8"/>
@@ -13581,7 +13610,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="B37" s="42" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="8"/>
@@ -13597,16 +13626,16 @@
     <row r="38" spans="1:12">
       <c r="B38" s="3"/>
       <c r="C38" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="8"/>
       <c r="H38" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="8"/>
@@ -13628,7 +13657,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="B40" s="42" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="8"/>
@@ -13636,7 +13665,7 @@
       <c r="F40" s="7"/>
       <c r="G40" s="8"/>
       <c r="H40" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="8"/>
@@ -13658,18 +13687,18 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="16" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="B46" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -13678,10 +13707,10 @@
     </row>
     <row r="48" spans="1:12">
       <c r="D48" s="7" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -13690,10 +13719,10 @@
     </row>
     <row r="50" spans="1:12">
       <c r="D50" s="7" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -13702,15 +13731,15 @@
     </row>
     <row r="52" spans="1:12">
       <c r="D52" s="7" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="16" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -13718,13 +13747,13 @@
     </row>
     <row r="56" spans="1:12">
       <c r="C56" s="16" t="s">
-        <v>601</v>
+        <v>1274</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -13732,13 +13761,13 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H57" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="L57" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -13746,13 +13775,13 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H58" t="s">
         <v>599</v>
       </c>
-      <c r="H58" t="s">
-        <v>602</v>
-      </c>
       <c r="L58" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -13760,13 +13789,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="69" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="H59" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="L59" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -13774,13 +13803,13 @@
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H60" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="L60" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -13788,13 +13817,13 @@
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="H61" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="L61" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -13802,10 +13831,10 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H62" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -13813,13 +13842,13 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="H63" t="s">
+        <v>738</v>
+      </c>
+      <c r="L63" t="s">
         <v>741</v>
-      </c>
-      <c r="L63" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -13827,13 +13856,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="H64" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="L64" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -13841,13 +13870,13 @@
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="H65" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="L65" s="63" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -13855,13 +13884,13 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="H66" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="L66" s="63" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -13869,13 +13898,13 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="H67" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="L67" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -13883,13 +13912,13 @@
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="H68" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="L68" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="M68" s="63"/>
     </row>
@@ -13898,10 +13927,13 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="H69" t="s">
-        <v>851</v>
+        <v>848</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1276</v>
       </c>
       <c r="M69" s="63"/>
     </row>
@@ -13910,10 +13942,10 @@
         <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="L70" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="M70" s="63"/>
     </row>
@@ -13922,13 +13954,13 @@
         <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="H71" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="L71" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="M71" s="63"/>
     </row>
@@ -13937,13 +13969,13 @@
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="H72" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="L72" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="M72" s="63"/>
     </row>
@@ -13952,10 +13984,10 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="L73" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="M73" s="63"/>
     </row>
@@ -13964,10 +13996,10 @@
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="L74" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="M74" s="63"/>
     </row>
@@ -13982,10 +14014,10 @@
     </row>
     <row r="78" spans="2:13">
       <c r="C78" s="27" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="I78" s="27" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -13993,13 +14025,13 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="80" spans="2:13">
@@ -14007,13 +14039,13 @@
         <v>2</v>
       </c>
       <c r="C80" s="57" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H80">
         <v>2</v>
       </c>
       <c r="I80" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -14021,13 +14053,13 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="H81">
         <v>3</v>
       </c>
       <c r="I81" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -14035,13 +14067,13 @@
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H82">
         <v>4</v>
       </c>
       <c r="I82" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -14049,13 +14081,13 @@
         <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H83">
         <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -14063,18 +14095,18 @@
         <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H84">
         <v>6</v>
       </c>
       <c r="I84" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="16" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -14082,10 +14114,10 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E89" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -14093,10 +14125,10 @@
         <v>2</v>
       </c>
       <c r="C90" t="s">
+        <v>612</v>
+      </c>
+      <c r="E90" t="s">
         <v>615</v>
-      </c>
-      <c r="E90" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -14104,10 +14136,10 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E91" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -14115,10 +14147,10 @@
         <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E92" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -14126,10 +14158,10 @@
         <v>5</v>
       </c>
       <c r="C93" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E93" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -14137,15 +14169,15 @@
         <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E94" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="16" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -14153,10 +14185,10 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D99" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -14164,15 +14196,15 @@
         <v>2</v>
       </c>
       <c r="C100" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D100" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="16" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -14180,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="C105" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -14188,7 +14220,7 @@
         <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -14196,7 +14228,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -14204,7 +14236,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -14212,7 +14244,7 @@
         <v>5</v>
       </c>
       <c r="C109" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -14220,7 +14252,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -14228,7 +14260,7 @@
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -14236,7 +14268,7 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -14244,7 +14276,7 @@
         <v>9</v>
       </c>
       <c r="C113" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -14252,7 +14284,7 @@
         <v>10</v>
       </c>
       <c r="C114" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -14260,7 +14292,7 @@
         <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -14271,7 +14303,7 @@
     <row r="119" spans="1:8">
       <c r="A119" s="16"/>
       <c r="B119" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -14279,13 +14311,13 @@
         <v>1</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G121">
         <v>2</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -14293,44 +14325,44 @@
         <v>3</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="G128">
         <v>4</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="C129" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H129" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="C130" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H130" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="H131" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="H132" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="H133" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -14338,23 +14370,23 @@
         <v>5</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G138">
         <v>6</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="139" spans="1:8">
-      <c r="C139" t="s">
-        <v>738</v>
+      <c r="C139" s="61" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="16" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -14362,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="C143" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -14370,7 +14402,7 @@
         <v>2</v>
       </c>
       <c r="C144" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -14378,169 +14410,169 @@
         <v>3</v>
       </c>
       <c r="C145" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="16" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="16" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="B150" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F150" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F151" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F152" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F153" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F154" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F155" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="16" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="B158" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F158" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="B159" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F159" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F160" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="B161" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F161" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="B162" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="F162" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="B163" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F163" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="B164" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F164" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="B165" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F165" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="B166" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="F166" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="16" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="B171" s="67" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C171" s="35"/>
       <c r="D171" s="35"/>
       <c r="E171" s="34"/>
       <c r="F171" s="68" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="G171" s="35"/>
       <c r="H171" s="34"/>
       <c r="I171" s="65" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="J171" s="35"/>
       <c r="K171" s="35"/>
@@ -14548,13 +14580,13 @@
     </row>
     <row r="172" spans="1:12">
       <c r="B172" s="67" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C172" s="35"/>
       <c r="D172" s="35"/>
       <c r="E172" s="34"/>
       <c r="F172" s="35" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="G172" s="35"/>
       <c r="H172" s="34"/>
@@ -14565,18 +14597,18 @@
     </row>
     <row r="173" spans="1:12">
       <c r="B173" s="67" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C173" s="35"/>
       <c r="D173" s="35"/>
       <c r="E173" s="34"/>
       <c r="F173" s="35" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="G173" s="35"/>
       <c r="H173" s="34"/>
       <c r="I173" s="67" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="J173" s="35"/>
       <c r="K173" s="35"/>
@@ -14584,7 +14616,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="B174" s="67" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C174" s="35"/>
       <c r="D174" s="35"/>
@@ -14595,7 +14627,7 @@
       <c r="G174" s="35"/>
       <c r="H174" s="34"/>
       <c r="I174" s="39" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="J174" s="35"/>
       <c r="K174" s="35"/>
@@ -14619,7 +14651,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="16" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -14627,7 +14659,7 @@
         <v>1</v>
       </c>
       <c r="C179" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -14635,7 +14667,7 @@
         <v>2</v>
       </c>
       <c r="C180" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -14643,7 +14675,7 @@
         <v>3</v>
       </c>
       <c r="C181" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -14651,7 +14683,7 @@
         <v>4</v>
       </c>
       <c r="C182" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -14659,12 +14691,12 @@
         <v>5</v>
       </c>
       <c r="C183" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="16" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B186" s="16"/>
     </row>
@@ -14673,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -14681,7 +14713,7 @@
         <v>2</v>
       </c>
       <c r="C189" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -14689,7 +14721,7 @@
         <v>3</v>
       </c>
       <c r="C190" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -14697,27 +14729,27 @@
         <v>4</v>
       </c>
       <c r="C191" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="16" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="B195" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="C196" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="C197" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -14739,31 +14771,31 @@
   <sheetData>
     <row r="2" spans="1:12">
       <c r="A2" s="16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="B3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="33" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="49" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="39" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="24">
@@ -14772,7 +14804,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="39" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="24">
@@ -14781,7 +14813,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="16" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C10" s="53">
         <v>46008</v>
@@ -14792,42 +14824,42 @@
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>591</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="52" t="s">
+        <v>587</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="D13" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="C13" s="49" t="s">
-        <v>513</v>
-      </c>
-      <c r="D13" s="49" t="s">
+      <c r="E13" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="F13" s="49" t="s">
         <v>589</v>
       </c>
-      <c r="E13" s="49" t="s">
-        <v>538</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>590</v>
-      </c>
       <c r="H13" s="52" t="s">
+        <v>587</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="J13" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="I13" s="49" t="s">
-        <v>513</v>
-      </c>
-      <c r="J13" s="49" t="s">
+      <c r="K13" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="L13" s="49" t="s">
         <v>589</v>
-      </c>
-      <c r="K13" s="49" t="s">
-        <v>538</v>
-      </c>
-      <c r="L13" s="49" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -14835,7 +14867,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D14" s="24">
         <v>0.3</v>
@@ -14851,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J14" s="24">
         <v>2</v>
@@ -14869,7 +14901,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D15" s="24">
         <v>1.8</v>
@@ -14885,7 +14917,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J15" s="24">
         <v>1</v>
@@ -14915,7 +14947,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J16" s="24">
         <v>1</v>
@@ -14992,24 +15024,24 @@
     </row>
     <row r="21" spans="1:12">
       <c r="B21" s="16" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="B22" s="52" t="s">
+        <v>587</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="D22" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="49" t="s">
-        <v>513</v>
-      </c>
-      <c r="D22" s="49" t="s">
+      <c r="E22" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="F22" s="49" t="s">
         <v>589</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>538</v>
-      </c>
-      <c r="F22" s="49" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -15017,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D23" s="24">
         <v>2.5</v>
@@ -15035,7 +15067,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D24" s="24">
         <v>1</v>
@@ -15053,7 +15085,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D25" s="24">
         <v>1</v>
@@ -15071,7 +15103,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
@@ -15108,41 +15140,41 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="B31" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="H32" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="B33" s="48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="6"/>
       <c r="E33" s="49" t="s">
+        <v>546</v>
+      </c>
+      <c r="F33" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="G33" s="49" t="s">
         <v>548</v>
       </c>
-      <c r="G33" s="49" t="s">
-        <v>549</v>
-      </c>
       <c r="H33" s="49" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="B34" s="39" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="34"/>
@@ -15161,7 +15193,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="B35" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8"/>
@@ -15180,7 +15212,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="B36" s="39" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C36" s="35"/>
       <c r="D36" s="34"/>
@@ -15199,7 +15231,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="B37" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="8"/>
@@ -15218,7 +15250,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="B38" s="39" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="34"/>
@@ -15237,12 +15269,12 @@
     </row>
     <row r="39" spans="1:8">
       <c r="B39" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="8"/>
       <c r="E39" s="24" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F39" s="24">
         <v>11</v>
@@ -15256,7 +15288,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="B40" s="39" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C40" s="35"/>
       <c r="D40" s="34"/>
@@ -15275,7 +15307,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="B41" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="8"/>
@@ -15294,7 +15326,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="B42" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C42" s="35"/>
       <c r="D42" s="34"/>
@@ -15313,7 +15345,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="B43" s="59" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="34"/>
@@ -15332,31 +15364,31 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="16" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="B47" s="48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="6"/>
       <c r="E47" s="51" t="s">
+        <v>561</v>
+      </c>
+      <c r="F47" s="49" t="s">
         <v>562</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="G47" s="49" t="s">
         <v>563</v>
       </c>
-      <c r="G47" s="49" t="s">
-        <v>564</v>
-      </c>
       <c r="H47" s="49" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="B48" s="39" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C48" s="35"/>
       <c r="D48" s="34"/>
@@ -15375,7 +15407,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="B49" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C49" s="35"/>
       <c r="D49" s="34"/>
@@ -15394,7 +15426,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="B50" s="39" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C50" s="35"/>
       <c r="D50" s="34"/>
@@ -15413,7 +15445,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="B51" s="39" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C51" s="35"/>
       <c r="D51" s="34"/>
@@ -15432,7 +15464,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="B52" s="39" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C52" s="35"/>
       <c r="D52" s="34"/>
@@ -15451,7 +15483,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="B53" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="8"/>
@@ -15470,7 +15502,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="B54" s="39" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C54" s="35"/>
       <c r="D54" s="34"/>
@@ -15489,7 +15521,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="B55" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="8"/>
@@ -15508,7 +15540,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="B56" s="39" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C56" s="35"/>
       <c r="D56" s="34"/>
@@ -15527,7 +15559,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="B57" s="59" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C57" s="35"/>
       <c r="D57" s="34"/>
@@ -15546,31 +15578,31 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="B61" s="48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="6"/>
       <c r="E61" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="F61" s="49" t="s">
         <v>562</v>
       </c>
-      <c r="F61" s="49" t="s">
+      <c r="G61" s="49" t="s">
         <v>563</v>
       </c>
-      <c r="G61" s="49" t="s">
-        <v>564</v>
-      </c>
       <c r="H61" s="49" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="B62" s="39" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C62" s="35"/>
       <c r="D62" s="34"/>
@@ -15589,7 +15621,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="B63" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="8"/>
@@ -15608,7 +15640,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="B64" s="39" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="34"/>
@@ -15627,7 +15659,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="B65" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="8"/>
@@ -15646,7 +15678,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="B66" s="39" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C66" s="35"/>
       <c r="D66" s="34"/>
@@ -15665,7 +15697,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="B67" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="11"/>
@@ -15684,7 +15716,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="B68" s="59" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C68" s="35"/>
       <c r="D68" s="34"/>
@@ -15703,31 +15735,31 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="16" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="B72" s="48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="6"/>
       <c r="E72" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="F72" s="49" t="s">
         <v>562</v>
       </c>
-      <c r="F72" s="49" t="s">
+      <c r="G72" s="49" t="s">
         <v>563</v>
       </c>
-      <c r="G72" s="49" t="s">
-        <v>564</v>
-      </c>
       <c r="H72" s="49" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="B73" s="39" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C73" s="35"/>
       <c r="D73" s="34"/>
@@ -15746,7 +15778,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="B74" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="8"/>
@@ -15765,7 +15797,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="39" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C75" s="35"/>
       <c r="D75" s="34"/>
@@ -15784,7 +15816,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="B76" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="8"/>
@@ -15803,7 +15835,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="B77" s="39" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C77" s="35"/>
       <c r="D77" s="34"/>
@@ -15835,240 +15867,240 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="70" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="16" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="70" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="70" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="16" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="C22" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="C25" s="16" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="D26" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="D27" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="D28" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="E29" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="E30" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="E31" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="D32" s="22" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="C34" s="16" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="D35" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="D36" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="D37" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="D38" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="D40" s="22" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="16" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="C44" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="C45" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="D46" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="D47" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="C48" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="49" spans="2:4">
       <c r="C49" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="51" spans="2:4">
       <c r="C51" s="22" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="53" spans="2:4">
       <c r="B53" s="16" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="54" spans="2:4">
       <c r="C54" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="D55" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="56" spans="2:4">
       <c r="D56" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="C58" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="59" spans="2:4">
       <c r="D59" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="D60" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="16" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="2:4">
@@ -16077,67 +16109,67 @@
     <row r="64" spans="2:4">
       <c r="B64" s="16"/>
       <c r="C64" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
     </row>
     <row r="65" spans="2:4">
       <c r="D65" s="71" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="C67" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="C68" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="C70" s="16" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="71" spans="2:4">
       <c r="D71" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="16" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="74" spans="2:4">
       <c r="C74" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="75" spans="2:4">
       <c r="C75" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="76" spans="2:4">
       <c r="C76" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="C77" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="79" spans="2:4">
       <c r="B79" s="16" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="80" spans="2:4">
       <c r="C80" s="22" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -16145,24 +16177,24 @@
     </row>
     <row r="82" spans="1:11">
       <c r="E82" s="74" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="F82" s="6"/>
       <c r="H82" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:11">
       <c r="C83" s="24" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E83" s="72"/>
       <c r="F83" s="8"/>
       <c r="H83" s="3"/>
       <c r="I83" s="8"/>
       <c r="K83" s="24" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -16179,468 +16211,468 @@
     </row>
     <row r="87" spans="1:11">
       <c r="B87" s="25" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C87" s="22"/>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="16" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="B90" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="B91" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="B92" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="B93" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="B94" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="16" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="F98" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="F99" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="I99" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="F100" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I100" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="F101" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="F102" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="I102" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="106" spans="2:9">
       <c r="B106" s="16" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="107" spans="2:9">
       <c r="C107" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="108" spans="2:9">
       <c r="C108" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="109" spans="2:9">
       <c r="C109" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="111" spans="2:9">
       <c r="B111" s="16" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="112" spans="2:9">
       <c r="C112" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="114" spans="2:4">
       <c r="C114" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="115" spans="2:4">
       <c r="D115" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="116" spans="2:4">
       <c r="D116" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="117" spans="2:4">
       <c r="D117" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="118" spans="2:4">
       <c r="C118" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="120" spans="2:4">
       <c r="B120" s="16" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="121" spans="2:4">
       <c r="B121" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="122" spans="2:4">
       <c r="C122" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="123" spans="2:4">
       <c r="C123" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="124" spans="2:4">
       <c r="C124" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
     </row>
     <row r="125" spans="2:4">
       <c r="C125" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="126" spans="2:4">
       <c r="C126" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="128" spans="2:4">
       <c r="B128" s="16" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="C129" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="C130" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="C131" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="C132" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="C133" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="C134" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="16" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="B137" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="C138" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="C139" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="C140" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="B142" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="C143" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="C144" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="C145" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="C146" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
     </row>
     <row r="147" spans="2:4">
       <c r="C147" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="16" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="C152" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="D153" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="D154" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="155" spans="2:4">
       <c r="D155" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="C157" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="D158" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="D159" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="D160" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="16" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="163" spans="2:4">
       <c r="C163" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="164" spans="2:4">
       <c r="D164" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="D165" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="D166" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="167" spans="2:4">
       <c r="D167" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="C169" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="D170" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="171" spans="2:4">
       <c r="D171" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="16" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="16"/>
       <c r="C174" s="16" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
     </row>
     <row r="175" spans="2:4">
       <c r="D175" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="176" spans="2:4">
       <c r="D176" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="C178" s="16" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="D179" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="D180" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="D181" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="C183" s="16" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="D184" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="D185" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="C187" s="16" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="D188" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="D189" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="D190" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="16" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="16" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="195" spans="1:13">
       <c r="B195" s="2" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="F195" s="5"/>
       <c r="G195" s="5"/>
@@ -16648,16 +16680,16 @@
     </row>
     <row r="196" spans="1:13">
       <c r="B196" s="3" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="F196" s="7"/>
       <c r="G196" s="7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="H196" s="8"/>
     </row>
@@ -16666,11 +16698,11 @@
       <c r="C197" s="10"/>
       <c r="D197" s="10"/>
       <c r="E197" s="10" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="F197" s="10"/>
       <c r="G197" s="10" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="H197" s="11"/>
     </row>
@@ -16688,7 +16720,7 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="66" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -16702,12 +16734,12 @@
     </row>
     <row r="200" spans="1:13">
       <c r="B200" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F200" s="5"/>
       <c r="G200" s="5"/>
@@ -16715,12 +16747,12 @@
     </row>
     <row r="201" spans="1:13">
       <c r="B201" s="4" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="10"/>
       <c r="E201" s="10" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F201" s="10"/>
       <c r="G201" s="10"/>
@@ -16736,12 +16768,12 @@
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="16" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="204" spans="1:13">
       <c r="B204" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
@@ -16766,7 +16798,7 @@
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
@@ -16780,22 +16812,22 @@
         <v>25</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="G206" s="10"/>
       <c r="H206" s="11"/>
       <c r="J206" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="16" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="209" spans="1:13">
       <c r="B209" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
@@ -16804,7 +16836,7 @@
       <c r="G209" s="5"/>
       <c r="H209" s="6"/>
       <c r="J209" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -16812,7 +16844,7 @@
       <c r="C210" s="10"/>
       <c r="D210" s="10"/>
       <c r="E210" s="10" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F210" s="10"/>
       <c r="G210" s="10"/>
@@ -16835,7 +16867,7 @@
     </row>
     <row r="212" spans="1:13">
       <c r="B212" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
@@ -16858,11 +16890,11 @@
     <row r="213" spans="1:13">
       <c r="B213" s="3"/>
       <c r="C213" s="7" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="D213" s="7"/>
       <c r="E213" s="7" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F213" s="7"/>
       <c r="G213" s="7"/>
@@ -16871,11 +16903,11 @@
     <row r="214" spans="1:13">
       <c r="B214" s="4"/>
       <c r="C214" s="10" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="D214" s="10"/>
       <c r="E214" s="10" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F214" s="10"/>
       <c r="G214" s="10"/>
@@ -16883,12 +16915,12 @@
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="16" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="218" spans="1:13">
       <c r="B218" s="48" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
@@ -16899,20 +16931,20 @@
     </row>
     <row r="219" spans="1:13">
       <c r="B219" s="3" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
       <c r="G219" s="7" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="H219" s="8"/>
     </row>
     <row r="220" spans="1:13">
       <c r="B220" s="77" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -16923,20 +16955,20 @@
     </row>
     <row r="221" spans="1:13">
       <c r="B221" s="72" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
       <c r="G221" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="H221" s="8"/>
     </row>
     <row r="222" spans="1:13">
       <c r="B222" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -16945,13 +16977,13 @@
         <v>134</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="H222" s="8"/>
     </row>
     <row r="223" spans="1:13">
       <c r="B223" s="3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -16960,39 +16992,39 @@
         <v>134</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="H223" s="8"/>
     </row>
     <row r="224" spans="1:13">
       <c r="B224" s="3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
       <c r="G224" s="7" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="H224" s="8"/>
     </row>
     <row r="225" spans="2:11">
       <c r="B225" s="78" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="10"/>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
       <c r="G225" s="10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H225" s="11"/>
     </row>
     <row r="227" spans="2:11">
       <c r="B227" s="48" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
@@ -17003,7 +17035,7 @@
     </row>
     <row r="228" spans="2:11">
       <c r="B228" s="77" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -17014,33 +17046,33 @@
     </row>
     <row r="229" spans="2:11">
       <c r="B229" s="72" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
       <c r="G229" s="7" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="H229" s="8"/>
     </row>
     <row r="230" spans="2:11">
       <c r="B230" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
       <c r="G230" s="7" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="H230" s="8"/>
     </row>
     <row r="231" spans="2:11">
       <c r="B231" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -17049,13 +17081,13 @@
         <v>134</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H231" s="8"/>
     </row>
     <row r="232" spans="2:11">
       <c r="B232" s="3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -17064,26 +17096,26 @@
         <v>134</v>
       </c>
       <c r="G232" s="7" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="H232" s="8"/>
     </row>
     <row r="233" spans="2:11">
       <c r="B233" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
       <c r="G233" s="7" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="H233" s="8"/>
     </row>
     <row r="234" spans="2:11">
       <c r="B234" s="4" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C234" s="10"/>
       <c r="D234" s="10"/>
@@ -17092,13 +17124,13 @@
         <v>134</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="H234" s="11"/>
     </row>
     <row r="236" spans="2:11">
       <c r="B236" s="48" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
@@ -17109,33 +17141,33 @@
     </row>
     <row r="237" spans="2:11">
       <c r="B237" s="72" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
       <c r="G237" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="H237" s="8"/>
     </row>
     <row r="238" spans="2:11">
       <c r="B238" s="4" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C238" s="10"/>
       <c r="D238" s="10"/>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
       <c r="G238" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="H238" s="11"/>
     </row>
     <row r="240" spans="2:11">
       <c r="B240" s="48" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
@@ -17147,33 +17179,33 @@
     </row>
     <row r="241" spans="2:8">
       <c r="B241" s="3" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
       <c r="G241" s="7" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H241" s="8"/>
     </row>
     <row r="242" spans="2:8">
       <c r="B242" s="73" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C242" s="10"/>
       <c r="D242" s="10"/>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
       <c r="G242" s="10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H242" s="11"/>
     </row>
     <row r="244" spans="2:8">
       <c r="B244" s="48" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
@@ -17184,7 +17216,7 @@
     </row>
     <row r="245" spans="2:8">
       <c r="B245" s="4" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="10"/>
@@ -17193,13 +17225,13 @@
         <v>134</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H245" s="11"/>
     </row>
     <row r="247" spans="2:8">
       <c r="B247" s="48" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
@@ -17210,20 +17242,20 @@
     </row>
     <row r="248" spans="2:8">
       <c r="B248" s="4" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C248" s="10"/>
       <c r="D248" s="10"/>
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
       <c r="G248" s="10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H248" s="11"/>
     </row>
     <row r="250" spans="2:8">
       <c r="B250" s="48" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
@@ -17234,25 +17266,25 @@
     </row>
     <row r="251" spans="2:8">
       <c r="B251" s="4" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C251" s="10"/>
       <c r="D251" s="10"/>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
       <c r="G251" s="10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H251" s="11"/>
     </row>
     <row r="254" spans="2:8">
       <c r="B254" s="16" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="256" spans="2:8">
       <c r="B256" s="48" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
@@ -17263,7 +17295,7 @@
     </row>
     <row r="257" spans="1:10">
       <c r="B257" s="3" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -17271,12 +17303,12 @@
       <c r="F257" s="7"/>
       <c r="G257" s="7"/>
       <c r="H257" s="8" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="258" spans="1:10">
       <c r="B258" s="4" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C258" s="10"/>
       <c r="D258" s="10"/>
@@ -17284,12 +17316,12 @@
       <c r="F258" s="10"/>
       <c r="G258" s="10"/>
       <c r="H258" s="11" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="260" spans="1:10">
       <c r="B260" s="48" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
@@ -17300,7 +17332,7 @@
     </row>
     <row r="261" spans="1:10">
       <c r="B261" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -17311,7 +17343,7 @@
     </row>
     <row r="262" spans="1:10">
       <c r="B262" s="3" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -17319,12 +17351,12 @@
       <c r="F262" s="7"/>
       <c r="G262" s="7"/>
       <c r="H262" s="8" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="263" spans="1:10">
       <c r="B263" s="3" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -17332,12 +17364,12 @@
       <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="264" spans="1:10">
       <c r="B264" s="80" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C264" s="10"/>
       <c r="D264" s="10"/>
@@ -17345,112 +17377,112 @@
       <c r="F264" s="10"/>
       <c r="G264" s="10"/>
       <c r="H264" s="11" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="J264" s="79" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="267" spans="1:10">
       <c r="A267" s="16" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="269" spans="1:10">
       <c r="B269" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="H269" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="270" spans="1:10">
       <c r="B270" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="H270" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="271" spans="1:10">
       <c r="B271" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="G271" t="s">
         <v>134</v>
       </c>
       <c r="H271" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="272" spans="1:10">
       <c r="B272" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="G272" t="s">
         <v>134</v>
       </c>
       <c r="H272" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="16" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="16"/>
       <c r="B275" s="16" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="276" spans="1:10">
       <c r="B276" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="H276" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J276" s="25" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="277" spans="1:10">
       <c r="B277" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H277" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="279" spans="1:10">
       <c r="B279" s="16" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="280" spans="1:10">
       <c r="B280" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="H280" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="281" spans="1:10">
       <c r="B281" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="H281" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="283" spans="1:10">
       <c r="B283" s="22" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="H283" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -17458,12 +17490,12 @@
     </row>
     <row r="286" spans="1:10">
       <c r="A286" s="16" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="287" spans="1:10">
       <c r="B287" s="25" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -17471,77 +17503,77 @@
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" s="16" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -17558,137 +17590,137 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="16" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="C6" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="C7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="C9" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="C12" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="C14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="C17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36" spans="3:3">
       <c r="C36" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -17703,15 +17735,15 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="E3" s="18" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -17719,7 +17751,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -17733,7 +17765,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E5">
         <v>60</v>
@@ -17747,7 +17779,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E6">
         <v>80</v>
@@ -17761,7 +17793,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E8">
         <v>180</v>
@@ -17775,7 +17807,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E9">
         <v>40</v>
@@ -17789,7 +17821,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E10">
         <v>12</v>
@@ -17803,7 +17835,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -17817,7 +17849,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -17831,7 +17863,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -17845,7 +17877,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E14">
         <v>12</v>
@@ -17861,7 +17893,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A5:K101"/>
+  <dimension ref="A5:K107"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
@@ -17873,28 +17905,28 @@
         <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="E6" s="84" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="F6" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="E7" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="F7" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="E8" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -18003,7 +18035,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="B27" s="75"/>
       <c r="C27" s="75"/>
@@ -18012,132 +18044,132 @@
     </row>
     <row r="28" spans="1:11">
       <c r="B28" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K28" t="s">
         <v>1172</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1174</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1175</v>
-      </c>
-      <c r="K28" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="B30" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="B31" s="24" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="B32" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="12" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="B36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="16" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="B39" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G39" t="s">
-        <v>1164</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="B40" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G40" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="B41" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G41" t="s">
         <v>1158</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="B42" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="G42" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="B43" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="G43" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="12" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="B46" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="12" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="B50" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="16" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -18146,203 +18178,203 @@
     <row r="55" spans="1:4">
       <c r="A55" s="16"/>
       <c r="B55" s="16" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="B56" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="D56" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D57" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="B58" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="D58" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="B59" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="D59" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="B60" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="D60" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="B61" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="D61" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="B62" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="D62" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="B63" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="D63" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="B64" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="D64" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="B65" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D65" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="B66" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="D66" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="16" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="B69" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="B70" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="B71" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="B72" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="B73" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="12" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="B76" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="B77" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="B79" s="12" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="C80" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="C82" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="83" spans="2:4">
       <c r="C83" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="C85" s="12" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="D86" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="87" spans="2:4">
       <c r="D87" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="89" spans="2:4">
       <c r="B89" s="12" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="90" spans="2:4">
       <c r="C90" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="D91" s="12" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="D92" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="94" spans="2:4">
       <c r="C94" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -18352,27 +18384,56 @@
     </row>
     <row r="96" spans="2:4">
       <c r="D96" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="B98" s="12" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="C99" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="C100" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="C101" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="98" spans="2:3">
-      <c r="B98" s="12" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3">
-      <c r="C99" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3">
-      <c r="C100" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3">
-      <c r="C101" t="s">
-        <v>1196</v>
+    <row r="104" spans="1:4">
+      <c r="A104" s="16" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="B105" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="B106" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="B107" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
@@ -18389,7 +18450,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -18400,7 +18461,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="61" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -18408,7 +18469,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -18416,7 +18477,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -18424,7 +18485,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -18432,7 +18493,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -18440,7 +18501,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -18448,135 +18509,135 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" t="s">
+        <v>755</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>756</v>
+      </c>
+      <c r="F11" t="s">
+        <v>757</v>
+      </c>
+      <c r="H11" t="s">
         <v>758</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="J11" t="s">
         <v>759</v>
-      </c>
-      <c r="F11" t="s">
-        <v>760</v>
-      </c>
-      <c r="H11" t="s">
-        <v>761</v>
-      </c>
-      <c r="J11" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C12" s="62"/>
       <c r="D12" s="62" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F12" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="G12" s="63"/>
       <c r="H12" s="25" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="J12" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C13" s="62"/>
       <c r="D13" s="62" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F13" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="G13" s="63"/>
       <c r="H13" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="J13" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C14" s="62"/>
       <c r="D14" s="62" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="F14" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="G14" s="63"/>
       <c r="H14" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="J14" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C15" s="62"/>
       <c r="D15" s="62" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F15" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="G15" s="63"/>
       <c r="H15" s="25" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="J15" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C16" s="62"/>
       <c r="D16" s="62" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F16" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="G16" s="63"/>
       <c r="H16" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="J16" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="B17" s="16" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="64" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="I17" s="16"/>
       <c r="J17" s="16" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -18584,7 +18645,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="53">
@@ -18603,7 +18664,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="16" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -18611,14 +18672,14 @@
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="16" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="F3" s="16"/>
       <c r="H3" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -18626,10 +18687,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="H4" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -18637,10 +18698,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="H5" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -18665,19 +18726,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="16" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="16"/>
       <c r="B101" s="94" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="16"/>
       <c r="B102" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -18688,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="93" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -18696,7 +18757,7 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -18704,7 +18765,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -18712,66 +18773,66 @@
         <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="16" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="16"/>
       <c r="B111" s="16" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="16"/>
       <c r="C112" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="G112" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="16"/>
       <c r="C113" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="G113" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="16"/>
       <c r="C114" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="G114" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="16"/>
       <c r="C115" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="G115" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="16"/>
       <c r="C116" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="G116" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -18780,7 +18841,7 @@
     <row r="118" spans="1:7">
       <c r="A118" s="16"/>
       <c r="C118" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -18791,7 +18852,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="16" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -18799,131 +18860,131 @@
     </row>
     <row r="123" spans="1:7">
       <c r="B123" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="B124" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="B125" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="B126" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="B128" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="C129" s="22" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="16" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="B132" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="B133" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="B134" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="B135" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="B136" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="B138" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="B140" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="C141" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G141" t="s">
         <v>1250</v>
-      </c>
-      <c r="G141" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="C142" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G142" t="s">
         <v>1251</v>
-      </c>
-      <c r="G142" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="C143" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G143" t="s">
         <v>1252</v>
-      </c>
-      <c r="G143" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="145" spans="2:3">
       <c r="B145" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="147" spans="2:3">
       <c r="B147" s="22" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="16" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="150" spans="2:3">
       <c r="C150" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="151" spans="2:3">
       <c r="C151" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="152" spans="2:3">
       <c r="C152" s="22" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="154" spans="2:3">
       <c r="C154" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1297">
   <si>
     <t>Мисъл</t>
   </si>
@@ -6413,6 +6413,104 @@
   </si>
   <si>
     <t>Възможност за изтегляне на добър кредит</t>
+  </si>
+  <si>
+    <t>Как мога да изкарам за 20 човека пари?</t>
+  </si>
+  <si>
+    <t>1. Като взема работа в голям обем като за 20 човека</t>
+  </si>
+  <si>
+    <t>2. Като намеря някой който да плати за тази работа</t>
+  </si>
+  <si>
+    <t>4. Готово</t>
+  </si>
+  <si>
+    <t>"Щом мога да свърша за 20 човека работа =&gt; мога да изкарам за 20 пари"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Свършвам работата </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>сам</t>
+    </r>
+  </si>
+  <si>
+    <t>Вереятност 5%</t>
+  </si>
+  <si>
+    <t>Вид работа: IT</t>
+  </si>
+  <si>
+    <t>Хора които я предлагат: 0</t>
+  </si>
+  <si>
+    <t>Вереятност 60%</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Като намеря </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>хора</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> които да я свършат</t>
+    </r>
+  </si>
+  <si>
+    <t>Вид работа: Електро, голям обект</t>
+  </si>
+  <si>
+    <t>Хора които я предлагат: 5-10</t>
+  </si>
+  <si>
+    <t>1. Да намеря голям пазар</t>
+  </si>
+  <si>
+    <t>3. Да намеря клиенти</t>
+  </si>
+  <si>
+    <t>Вариант 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Да намеря от къде да купувам </t>
+  </si>
+  <si>
+    <t>2. Като намеря някой, който да плати за тази работа</t>
+  </si>
+  <si>
+    <t>Вид работа: Търговия</t>
+  </si>
+  <si>
+    <t>Вереятност 10%</t>
   </si>
 </sst>
 </file>
@@ -6833,7 +6931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6953,6 +7051,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13305,7 +13404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M197"/>
+  <dimension ref="A2:M222"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
@@ -13830,7 +13929,7 @@
       <c r="B62">
         <v>6</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="16" t="s">
         <v>653</v>
       </c>
       <c r="H62" t="s">
@@ -13983,7 +14082,7 @@
       <c r="B73">
         <v>17</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="16" t="s">
         <v>849</v>
       </c>
       <c r="L73" t="s">
@@ -13995,7 +14094,7 @@
       <c r="B74">
         <v>18</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="16" t="s">
         <v>851</v>
       </c>
       <c r="L74" t="s">
@@ -14732,25 +14831,250 @@
         <v>837</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:11">
       <c r="A194" s="16" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:11">
       <c r="B195" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:11">
       <c r="C196" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:11">
       <c r="C197" t="s">
         <v>855</v>
       </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" s="16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="B201" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="B202" s="16" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="B203" s="95"/>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="B204" s="48" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C204" s="5"/>
+      <c r="D204" s="5"/>
+      <c r="E204" s="6"/>
+      <c r="G204" s="48" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5"/>
+      <c r="J204" s="6"/>
+      <c r="K204" s="7"/>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="B205" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="8"/>
+      <c r="F205" t="s">
+        <v>134</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H205" s="7"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="8"/>
+      <c r="K205" s="7"/>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="B206" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="8"/>
+      <c r="F206" t="s">
+        <v>134</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H206" s="7"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="8"/>
+      <c r="K206" s="7"/>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="B207" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="8"/>
+      <c r="G207" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H207" s="7"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="8"/>
+      <c r="K207" s="7"/>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="B208" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="8"/>
+      <c r="G208" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H208" s="7"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="8"/>
+      <c r="K208" s="7"/>
+    </row>
+    <row r="209" spans="2:11">
+      <c r="B209" s="3"/>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="8"/>
+      <c r="G209" s="3"/>
+      <c r="H209" s="7"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="8"/>
+      <c r="K209" s="7"/>
+    </row>
+    <row r="210" spans="2:11">
+      <c r="B210" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="8"/>
+      <c r="G210" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H210" s="7"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="7"/>
+    </row>
+    <row r="211" spans="2:11">
+      <c r="B211" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="8"/>
+      <c r="G211" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H211" s="7"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="7"/>
+    </row>
+    <row r="212" spans="2:11">
+      <c r="B212" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C212" s="10"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="11"/>
+      <c r="G212" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H212" s="10"/>
+      <c r="I212" s="10"/>
+      <c r="J212" s="11"/>
+      <c r="K212" s="7"/>
+    </row>
+    <row r="214" spans="2:11">
+      <c r="B214" s="48" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="6"/>
+    </row>
+    <row r="215" spans="2:11">
+      <c r="B215" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="8"/>
+    </row>
+    <row r="216" spans="2:11">
+      <c r="B216" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="8"/>
+    </row>
+    <row r="217" spans="2:11">
+      <c r="B217" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="8"/>
+    </row>
+    <row r="218" spans="2:11">
+      <c r="B218" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7"/>
+      <c r="E218" s="8"/>
+    </row>
+    <row r="219" spans="2:11">
+      <c r="B219" s="3"/>
+      <c r="C219" s="7"/>
+      <c r="D219" s="7"/>
+      <c r="E219" s="8"/>
+    </row>
+    <row r="220" spans="2:11">
+      <c r="B220" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="8"/>
+    </row>
+    <row r="221" spans="2:11">
+      <c r="B221" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="8"/>
+    </row>
+    <row r="222" spans="2:11">
+      <c r="B222" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C222" s="10"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/life.xlsx
+++ b/life.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1338">
   <si>
     <t>Мисъл</t>
   </si>
@@ -6511,18 +6511,149 @@
   </si>
   <si>
     <t>Вереятност 10%</t>
+  </si>
+  <si>
+    <t>Бизнес прозрения</t>
+  </si>
+  <si>
+    <t>Какво им трябва?</t>
+  </si>
+  <si>
+    <t>технически съппорт</t>
+  </si>
+  <si>
+    <t>документално легализиране на надценката</t>
+  </si>
+  <si>
+    <t>бързо доставяне на материалите</t>
+  </si>
+  <si>
+    <t>доставка до обекта - понякога</t>
+  </si>
+  <si>
+    <t>качествени материали</t>
+  </si>
+  <si>
+    <t>оферти</t>
+  </si>
+  <si>
+    <t>редовни поръчки</t>
+  </si>
+  <si>
+    <t>1. Да продаваш на майстори(Тони, Краси, Влади Пешев, Иван Луксера, Владо Кади)</t>
+  </si>
+  <si>
+    <t>прадаваш на -20%, не на -40%</t>
+  </si>
+  <si>
+    <t>Какво ще получиш?</t>
+  </si>
+  <si>
+    <t>2. Да извършваш ел.услуги на частни клиенти</t>
+  </si>
+  <si>
+    <t>качествено свършена работа</t>
+  </si>
+  <si>
+    <t>нормални цени</t>
+  </si>
+  <si>
+    <t>отзоваване в нормален срок</t>
+  </si>
+  <si>
+    <t>гаранция и поеманена на бъдеща повреда</t>
+  </si>
+  <si>
+    <t>спокойствие че ще свършиш работата перфектно</t>
+  </si>
+  <si>
+    <t>бързи и добри пари</t>
+  </si>
+  <si>
+    <t>печалба от труд и материли</t>
+  </si>
+  <si>
+    <t>управление на времето си</t>
+  </si>
+  <si>
+    <t>възможност за увеличаване на клиентите</t>
+  </si>
+  <si>
+    <t>venv in the brain</t>
+  </si>
+  <si>
+    <t>1. Живея в изобилие</t>
+  </si>
+  <si>
+    <t>3. Имам безкрайни възможности</t>
+  </si>
+  <si>
+    <t>5. Живея без да се стравнявам, съобразявам и влияя от мнението на другите</t>
+  </si>
+  <si>
+    <t>6. Правя това което мен ме прави щастлив</t>
+  </si>
+  <si>
+    <t>4. Живея най-щастливия си живот</t>
+  </si>
+  <si>
+    <t>7. Живея в спокойствие и хармония със себе си</t>
+  </si>
+  <si>
+    <t>8. Живея със самочувствие и гордост от себе си</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Живея е силно и здраво тяло </t>
+  </si>
+  <si>
+    <t>12. Живея с любов в сърцето си</t>
+  </si>
+  <si>
+    <t>10. Живея със смел и безстрашен характер</t>
+  </si>
+  <si>
+    <t>11. Живея с солидни бойни умения, които ми дават смелост за всичко, което искам да направя</t>
+  </si>
+  <si>
+    <t>2. Живея в перфектно здраве</t>
+  </si>
+  <si>
+    <t>13. Живея със огромни знания, които хората търсят и искат да платят за тях</t>
+  </si>
+  <si>
+    <t>14. Живея без хора които да ме карат да се чувствам малък</t>
+  </si>
+  <si>
+    <t>15. Живея и знам че проблемите ми са временни</t>
+  </si>
+  <si>
+    <t>16. Подобрявам себе си всеки ден и се вълнувам искрено от постигането на целите си</t>
+  </si>
+  <si>
+    <t>17. хобито ми е да подобрявам себе си</t>
+  </si>
+  <si>
+    <t>18. Живея без да съжалявам за миналото и бе з да страхувам от бъдещето</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6948,93 +7079,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -7049,9 +7180,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13404,7 +13535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M222"/>
+  <dimension ref="A2:M275"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
@@ -15075,6 +15206,221 @@
       <c r="C222" s="10"/>
       <c r="D222" s="10"/>
       <c r="E222" s="11"/>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="16" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="B226" s="16" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="C228" s="16" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="D229" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="D230" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="D231" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="D232" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="D233" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="D234" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="C236" s="16" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="D237" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="D238" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="B240" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="C242" s="16" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="D243" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="D244" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="D245" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="D246" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="D247" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="C249" s="16" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="D250" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="D251" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="D252" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="D253" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="16" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" t="s">
+        <v>1337</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/life.xlsx
+++ b/life.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1340">
   <si>
     <t>Мисъл</t>
   </si>
@@ -6588,12 +6588,6 @@
     <t>3. Имам безкрайни възможности</t>
   </si>
   <si>
-    <t>5. Живея без да се стравнявам, съобразявам и влияя от мнението на другите</t>
-  </si>
-  <si>
-    <t>6. Правя това което мен ме прави щастлив</t>
-  </si>
-  <si>
     <t>4. Живея най-щастливия си живот</t>
   </si>
   <si>
@@ -6627,13 +6621,25 @@
     <t>15. Живея и знам че проблемите ми са временни</t>
   </si>
   <si>
-    <t>16. Подобрявам себе си всеки ден и се вълнувам искрено от постигането на целите си</t>
-  </si>
-  <si>
-    <t>17. хобито ми е да подобрявам себе си</t>
-  </si>
-  <si>
-    <t>18. Живея без да съжалявам за миналото и бе з да страхувам от бъдещето</t>
+    <t xml:space="preserve">19. Болката е моя приятелка, която ми помага да постигна целите си </t>
+  </si>
+  <si>
+    <t>20. Тази витруална среда ми е напълно достатъчна за да съм щастлив без външно обстоятелство</t>
+  </si>
+  <si>
+    <t>5. Живея без да се сравнявам, съобразявам и влияя от мнението на другите</t>
+  </si>
+  <si>
+    <t>6. Правя това което ме прави щастлив</t>
+  </si>
+  <si>
+    <t>17. Хобито ми е да подобрявам себе си</t>
+  </si>
+  <si>
+    <t>16. Вълнувам се искрено от постигането на целите си</t>
+  </si>
+  <si>
+    <t>18. Живея без да съжалявам за миналото и без да страхувам от бъдещето</t>
   </si>
 </sst>
 </file>
@@ -13535,7 +13541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M275"/>
+  <dimension ref="A2:M277"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
@@ -15339,7 +15345,7 @@
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="260" spans="2:2">
@@ -15349,77 +15355,87 @@
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>1337</v>
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" t="s">
+        <v>1334</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="1467">
   <si>
     <t>Мисъл</t>
   </si>
@@ -5670,9 +5670,6 @@
     <t>Тъй като сключих договор за план Комфорт на който е 12 месеца без такса и 3,5 €/месец след 1 година. Трябва след 12 месеца да сменя плана си от Комфорт на обикновен</t>
   </si>
   <si>
-    <t>Лв</t>
-  </si>
-  <si>
     <t>€</t>
   </si>
   <si>
@@ -5685,9 +5682,6 @@
     <t>Вид задача</t>
   </si>
   <si>
-    <t>Да дам на Петя удостоверението</t>
-  </si>
-  <si>
     <t>Гуми</t>
   </si>
   <si>
@@ -6640,6 +6634,414 @@
   </si>
   <si>
     <t>18. Живея без да съжалявам за миналото и без да страхувам от бъдещето</t>
+  </si>
+  <si>
+    <t>Цел 78 кг</t>
+  </si>
+  <si>
+    <t>Основни цели</t>
+  </si>
+  <si>
+    <t>Калории: ~2900–3300 kcal/ден</t>
+  </si>
+  <si>
+    <t>Протеин: 140–160 г</t>
+  </si>
+  <si>
+    <t>Въглехидрати: 350–450 г</t>
+  </si>
+  <si>
+    <t>Мазнини: 70–90 г</t>
+  </si>
+  <si>
+    <t>Вода: 2.5–3.5 л</t>
+  </si>
+  <si>
+    <t>Ден 1</t>
+  </si>
+  <si>
+    <t>100 г овес</t>
+  </si>
+  <si>
+    <t>300 мл прясно мляко</t>
+  </si>
+  <si>
+    <t>1 банан</t>
+  </si>
+  <si>
+    <t>30 г фъстъчено масло</t>
+  </si>
+  <si>
+    <t>3 яйца</t>
+  </si>
+  <si>
+    <t>кисело мляко</t>
+  </si>
+  <si>
+    <t>шепа ядки</t>
+  </si>
+  <si>
+    <t>мед</t>
+  </si>
+  <si>
+    <t>200 г пилешко</t>
+  </si>
+  <si>
+    <t>150 г ориз</t>
+  </si>
+  <si>
+    <t>салата + зехтин</t>
+  </si>
+  <si>
+    <t>Преди тренировка</t>
+  </si>
+  <si>
+    <t>банан</t>
+  </si>
+  <si>
+    <t>2 филии с фъстъчено масло</t>
+  </si>
+  <si>
+    <t>200 г телешко/кайма</t>
+  </si>
+  <si>
+    <t>картофи</t>
+  </si>
+  <si>
+    <t>зеленчуци</t>
+  </si>
+  <si>
+    <t>Тренировка</t>
+  </si>
+  <si>
+    <t>Лицеви опори — 4x15</t>
+  </si>
+  <si>
+    <t>Кофички — 4x8–12</t>
+  </si>
+  <si>
+    <t>Набирания — 4xмакс</t>
+  </si>
+  <si>
+    <t>Австралийски набирания — 3x12</t>
+  </si>
+  <si>
+    <t>Лицеви с тесен хват — 3x12</t>
+  </si>
+  <si>
+    <t>Планк — 3x1 мин</t>
+  </si>
+  <si>
+    <t>След тренировка</t>
+  </si>
+  <si>
+    <t>500 мл мляко</t>
+  </si>
+  <si>
+    <t>Ден 2</t>
+  </si>
+  <si>
+    <t>4 яйца</t>
+  </si>
+  <si>
+    <t>сирене</t>
+  </si>
+  <si>
+    <t>хляб</t>
+  </si>
+  <si>
+    <t>домати</t>
+  </si>
+  <si>
+    <t>200 г свинско/пилешко</t>
+  </si>
+  <si>
+    <t>150 г картофи</t>
+  </si>
+  <si>
+    <t>салата</t>
+  </si>
+  <si>
+    <t>ориз + яйца</t>
+  </si>
+  <si>
+    <t>или</t>
+  </si>
+  <si>
+    <t>протеин + банан</t>
+  </si>
+  <si>
+    <t>паста с кайма</t>
+  </si>
+  <si>
+    <t>Тренировка - Крака</t>
+  </si>
+  <si>
+    <t>Тренировка Гърди + Лостове</t>
+  </si>
+  <si>
+    <t>Клекове — 5x8–10</t>
+  </si>
+  <si>
+    <t>Български клек — 4x10</t>
+  </si>
+  <si>
+    <t>Напади — 3x12</t>
+  </si>
+  <si>
+    <t>Глутеус мост — 4x12</t>
+  </si>
+  <si>
+    <t>Прасци — 4x20</t>
+  </si>
+  <si>
+    <t>Корем — 10 мин</t>
+  </si>
+  <si>
+    <t>Ден 3</t>
+  </si>
+  <si>
+    <t>Хранене</t>
+  </si>
+  <si>
+    <t>Подобно на Ден 1, но увеличи ориза/пастата</t>
+  </si>
+  <si>
+    <t>Гръб + Бицепс</t>
+  </si>
+  <si>
+    <t>Набирания широк хват — 5xмакс</t>
+  </si>
+  <si>
+    <t>Chin-ups — 4xмакс</t>
+  </si>
+  <si>
+    <t>Гребане с дъмбел/ластици — 4x10</t>
+  </si>
+  <si>
+    <t>Австралийски набирания — 4x12</t>
+  </si>
+  <si>
+    <t>Сгъване за бицепс — 4x12</t>
+  </si>
+  <si>
+    <t>Hammer curls — 3x12</t>
+  </si>
+  <si>
+    <t>Повдигане на крака от вис — 4x12</t>
+  </si>
+  <si>
+    <t>Ден 4</t>
+  </si>
+  <si>
+    <t>Почивка + Храна</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Фокус</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: повече калории, възстановяване</t>
+    </r>
+  </si>
+  <si>
+    <t>Яж:</t>
+  </si>
+  <si>
+    <t>ориз</t>
+  </si>
+  <si>
+    <t>паста</t>
+  </si>
+  <si>
+    <t>месо</t>
+  </si>
+  <si>
+    <t>ядки</t>
+  </si>
+  <si>
+    <t>плодове</t>
+  </si>
+  <si>
+    <t>Ден 5</t>
+  </si>
+  <si>
+    <t>Рамо + Експлозивност</t>
+  </si>
+  <si>
+    <t>Pike push-ups — 4x10</t>
+  </si>
+  <si>
+    <t>Раменни преси — 4x10</t>
+  </si>
+  <si>
+    <t>Странично вдигане — 4x15</t>
+  </si>
+  <si>
+    <t>Explosive push-ups — 4x8</t>
+  </si>
+  <si>
+    <t>Burpees — 3x15</t>
+  </si>
+  <si>
+    <t>Повече въглехидрати:</t>
+  </si>
+  <si>
+    <t>овес</t>
+  </si>
+  <si>
+    <t>банани</t>
+  </si>
+  <si>
+    <t>Ден 6</t>
+  </si>
+  <si>
+    <t>Бокс (1.5 часа)</t>
+  </si>
+  <si>
+    <t>Това е сериозно кардио, така че:</t>
+  </si>
+  <si>
+    <t>не режи храната;</t>
+  </si>
+  <si>
+    <t>яж повече въглехидрати</t>
+  </si>
+  <si>
+    <t>Преди бокс</t>
+  </si>
+  <si>
+    <t>овес + банан</t>
+  </si>
+  <si>
+    <t>кафе (по желание)</t>
+  </si>
+  <si>
+    <t>След бокс</t>
+  </si>
+  <si>
+    <t>ориз + месо</t>
+  </si>
+  <si>
+    <t>шейк + банан + сандвич</t>
+  </si>
+  <si>
+    <t>Допълнително</t>
+  </si>
+  <si>
+    <t>Лека тренировка:</t>
+  </si>
+  <si>
+    <t>набирания 3 серии</t>
+  </si>
+  <si>
+    <t>кофички 3 серии</t>
+  </si>
+  <si>
+    <t>стречинг</t>
+  </si>
+  <si>
+    <t>Ден 7</t>
+  </si>
+  <si>
+    <t>Цяло тяло</t>
+  </si>
+  <si>
+    <t>Кофички — 4xмакс</t>
+  </si>
+  <si>
+    <t>Клекове — 4x15</t>
+  </si>
+  <si>
+    <t>Лицеви — 4x20</t>
+  </si>
+  <si>
+    <t>Планк — 3 серии</t>
+  </si>
+  <si>
+    <t>“Cheat meal” е ок:</t>
+  </si>
+  <si>
+    <t>бургер</t>
+  </si>
+  <si>
+    <t>пица</t>
+  </si>
+  <si>
+    <t>Но дръж протеина висок</t>
+  </si>
+  <si>
+    <t>Най-важните храни за качване</t>
+  </si>
+  <si>
+    <t>Евтини и ефективни</t>
+  </si>
+  <si>
+    <t>пилешко</t>
+  </si>
+  <si>
+    <t>кайма</t>
+  </si>
+  <si>
+    <t>фъстъчено масло</t>
+  </si>
+  <si>
+    <t>Как да разбереш дали работи</t>
+  </si>
+  <si>
+    <t>Следи:</t>
+  </si>
+  <si>
+    <t>тегло сутрин;</t>
+  </si>
+  <si>
+    <t>снимки;</t>
+  </si>
+  <si>
+    <t>сила.</t>
+  </si>
+  <si>
+    <t>Ако:</t>
+  </si>
+  <si>
+    <t>качваш сила;</t>
+  </si>
+  <si>
+    <t>качваш 1–2 кг месечно;</t>
+  </si>
+  <si>
+    <t>значи си в правилната посока.</t>
+  </si>
+  <si>
+    <t>Важни цели за първите 6 месеца</t>
+  </si>
+  <si>
+    <t>Опитай да стигнеш:</t>
+  </si>
+  <si>
+    <t>12–15 набирания;</t>
+  </si>
+  <si>
+    <t>20+ кофички;</t>
+  </si>
+  <si>
+    <t>100+ клекове;</t>
   </si>
 </sst>
 </file>
@@ -7068,7 +7470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7189,6 +7591,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13312,23 +13715,23 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D4" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="86" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -13377,10 +13780,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="B10" s="89" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -13392,10 +13795,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="89" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -13407,10 +13810,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="90" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -13423,7 +13826,7 @@
     <row r="13" spans="1:11">
       <c r="C13" s="62"/>
       <c r="D13" s="3" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -13436,7 +13839,7 @@
     <row r="14" spans="1:11">
       <c r="C14" s="62"/>
       <c r="D14" s="3" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -13449,7 +13852,7 @@
     <row r="15" spans="1:11">
       <c r="C15" s="62"/>
       <c r="D15" s="3" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -13462,7 +13865,7 @@
     <row r="16" spans="1:11">
       <c r="C16" s="62"/>
       <c r="D16" s="3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -13475,7 +13878,7 @@
     <row r="17" spans="3:11">
       <c r="C17" s="62"/>
       <c r="D17" s="3" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -13488,7 +13891,7 @@
     <row r="18" spans="3:11">
       <c r="C18" s="62"/>
       <c r="D18" s="3" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -13501,7 +13904,7 @@
     <row r="19" spans="3:11">
       <c r="C19" s="62"/>
       <c r="D19" s="3" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -13514,7 +13917,7 @@
     <row r="20" spans="3:11">
       <c r="C20" s="62"/>
       <c r="D20" s="4" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -13530,7 +13933,7 @@
     </row>
     <row r="22" spans="3:11">
       <c r="C22" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G22" s="63"/>
     </row>
@@ -13671,7 +14074,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="B24" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -13983,7 +14386,7 @@
     </row>
     <row r="56" spans="1:12">
       <c r="C56" s="16" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>598</v>
@@ -14011,7 +14414,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="H58" t="s">
         <v>599</v>
@@ -14169,7 +14572,7 @@
         <v>848</v>
       </c>
       <c r="L69" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="M69" s="63"/>
     </row>
@@ -14995,12 +15398,12 @@
     </row>
     <row r="201" spans="1:11">
       <c r="B201" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="202" spans="1:11">
       <c r="B202" s="16" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -15008,13 +15411,13 @@
     </row>
     <row r="204" spans="1:11">
       <c r="B204" s="48" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="6"/>
       <c r="G204" s="48" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
@@ -15023,7 +15426,7 @@
     </row>
     <row r="205" spans="1:11">
       <c r="B205" s="3" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -15032,7 +15435,7 @@
         <v>134</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="H205" s="7"/>
       <c r="I205" s="7"/>
@@ -15041,7 +15444,7 @@
     </row>
     <row r="206" spans="1:11">
       <c r="B206" s="3" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -15050,7 +15453,7 @@
         <v>134</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H206" s="7"/>
       <c r="I206" s="7"/>
@@ -15059,13 +15462,13 @@
     </row>
     <row r="207" spans="1:11">
       <c r="B207" s="3" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
       <c r="E207" s="8"/>
       <c r="G207" s="3" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="H207" s="7"/>
       <c r="I207" s="7"/>
@@ -15074,13 +15477,13 @@
     </row>
     <row r="208" spans="1:11">
       <c r="B208" s="3" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
       <c r="E208" s="8"/>
       <c r="G208" s="3" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H208" s="7"/>
       <c r="I208" s="7"/>
@@ -15100,13 +15503,13 @@
     </row>
     <row r="210" spans="2:11">
       <c r="B210" s="3" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
       <c r="E210" s="8"/>
       <c r="G210" s="3" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="7"/>
@@ -15115,13 +15518,13 @@
     </row>
     <row r="211" spans="2:11">
       <c r="B211" s="3" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
       <c r="E211" s="8"/>
       <c r="G211" s="3" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="7"/>
@@ -15130,13 +15533,13 @@
     </row>
     <row r="212" spans="2:11">
       <c r="B212" s="4" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C212" s="10"/>
       <c r="D212" s="10"/>
       <c r="E212" s="11"/>
       <c r="G212" s="4" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H212" s="10"/>
       <c r="I212" s="10"/>
@@ -15145,7 +15548,7 @@
     </row>
     <row r="214" spans="2:11">
       <c r="B214" s="48" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
@@ -15153,7 +15556,7 @@
     </row>
     <row r="215" spans="2:11">
       <c r="B215" s="3" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -15161,7 +15564,7 @@
     </row>
     <row r="216" spans="2:11">
       <c r="B216" s="3" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -15169,7 +15572,7 @@
     </row>
     <row r="217" spans="2:11">
       <c r="B217" s="3" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -15177,7 +15580,7 @@
     </row>
     <row r="218" spans="2:11">
       <c r="B218" s="3" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -15191,7 +15594,7 @@
     </row>
     <row r="220" spans="2:11">
       <c r="B220" s="3" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -15199,7 +15602,7 @@
     </row>
     <row r="221" spans="2:11">
       <c r="B221" s="3" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -15207,7 +15610,7 @@
     </row>
     <row r="222" spans="2:11">
       <c r="B222" s="4" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C222" s="10"/>
       <c r="D222" s="10"/>
@@ -15215,227 +15618,227 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="16" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="B226" s="16" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="C228" s="16" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="D229" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="D230" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="D231" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="D232" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="D233" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="D234" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="C236" s="16" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="D237" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="D238" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="B240" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="C242" s="16" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="D243" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="D244" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="D245" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="D246" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="D247" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="C249" s="16" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="D250" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="D251" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="D252" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="D253" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="16" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -15447,7 +15850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:L77"/>
+  <dimension ref="A2:L226"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -16538,8 +16941,737 @@
         <v>40</v>
       </c>
     </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="16" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="B82" s="16" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="C83" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="C84" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="C85" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="C86" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="C87" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="B89" s="16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="C90" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="I90" s="16" t="s">
+        <v>1357</v>
+      </c>
+      <c r="K90" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="C91" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E91" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I91" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K91" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L91" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="C92" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="C93" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E93" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K93" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="C94" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="C95" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="C97" s="16" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="D98" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="D99" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
+      <c r="D100" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="D101" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="D102" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="D103" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="16" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="C106" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="C107" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="C108" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G108" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="C109" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E109" s="25" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="C110" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="C112" s="16" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="D113" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="D114" s="25" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="D115" s="25" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="D116" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="D117" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="D118" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="16" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="C121" s="16" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="D122" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="C124" s="16" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="D125" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="D127" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="D128" s="25" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5">
+      <c r="D129" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5">
+      <c r="D130" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5">
+      <c r="D131" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5">
+      <c r="D132" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5">
+      <c r="D133" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5">
+      <c r="B135" s="16" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5">
+      <c r="C136" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5">
+      <c r="C137" s="96" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5">
+      <c r="C139" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5">
+      <c r="D140" t="s">
+        <v>790</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5">
+      <c r="D141" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5">
+      <c r="D142" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E142" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5">
+      <c r="D143" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="16" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="C146" s="16" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="C147" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="C149" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="C150" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="C151" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="C152" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="C153" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="C154" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="C156" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="D157" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="D158" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="D159" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="D160" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5">
+      <c r="D161" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5">
+      <c r="B162" s="16" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5">
+      <c r="C164" s="16" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5">
+      <c r="D165" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5">
+      <c r="E166" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5">
+      <c r="E167" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5">
+      <c r="C169" s="16" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5">
+      <c r="D170" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5">
+      <c r="D171" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5">
+      <c r="D172" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5">
+      <c r="C174" s="16" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5">
+      <c r="D175" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5">
+      <c r="D176" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="D177" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="C179" s="16" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="D180" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="D181" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="D182" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="D183" s="25" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="16" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="C185" s="16" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="C186" s="96" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="D187" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="D188" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="D189" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="D190" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="D191" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="D192" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="C194" s="16" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="D195" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="D196" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="D197" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="D198" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="D200" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="16" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="C204" s="16" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="C205" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="C206" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="C207" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="C208" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5">
+      <c r="C209" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5">
+      <c r="C210" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5">
+      <c r="C211" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5">
+      <c r="C212" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5">
+      <c r="C213" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5">
+      <c r="C214" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5">
+      <c r="B216" s="16" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5">
+      <c r="C217" s="16" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E217" s="16" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5">
+      <c r="C218" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5">
+      <c r="C219" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5">
+      <c r="C220" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5">
+      <c r="B222" s="16" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5">
+      <c r="C223" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5">
+      <c r="D224" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="225" spans="4:4">
+      <c r="D225" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="226" spans="4:4">
+      <c r="D226" t="s">
+        <v>1466</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18189,77 +19321,77 @@
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" s="16" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -18425,11 +19557,9 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
         <v>1101</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18439,9 +19569,6 @@
       <c r="B4" t="s">
         <v>777</v>
       </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
       <c r="F4">
         <v>20</v>
       </c>
@@ -18453,9 +19580,6 @@
       <c r="B5" t="s">
         <v>778</v>
       </c>
-      <c r="E5">
-        <v>60</v>
-      </c>
       <c r="F5">
         <v>40</v>
       </c>
@@ -18467,9 +19591,6 @@
       <c r="B6" t="s">
         <v>779</v>
       </c>
-      <c r="E6">
-        <v>80</v>
-      </c>
       <c r="F6">
         <v>50</v>
       </c>
@@ -18481,11 +19602,8 @@
       <c r="B8" t="s">
         <v>780</v>
       </c>
-      <c r="E8">
-        <v>180</v>
-      </c>
       <c r="F8">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18495,9 +19613,6 @@
       <c r="B9" t="s">
         <v>781</v>
       </c>
-      <c r="E9">
-        <v>40</v>
-      </c>
       <c r="F9">
         <v>20</v>
       </c>
@@ -18509,9 +19624,6 @@
       <c r="B10" t="s">
         <v>782</v>
       </c>
-      <c r="E10">
-        <v>12</v>
-      </c>
       <c r="F10">
         <v>8</v>
       </c>
@@ -18523,9 +19635,6 @@
       <c r="B11" t="s">
         <v>785</v>
       </c>
-      <c r="E11">
-        <v>7</v>
-      </c>
       <c r="F11">
         <v>4</v>
       </c>
@@ -18537,9 +19646,6 @@
       <c r="B12" t="s">
         <v>786</v>
       </c>
-      <c r="E12">
-        <v>8</v>
-      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -18551,9 +19657,6 @@
       <c r="B13" t="s">
         <v>784</v>
       </c>
-      <c r="E13">
-        <v>9</v>
-      </c>
       <c r="F13">
         <v>5</v>
       </c>
@@ -18564,9 +19667,6 @@
       </c>
       <c r="B14" t="s">
         <v>783</v>
-      </c>
-      <c r="E14">
-        <v>12</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -18591,28 +19691,28 @@
         <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="E6" s="84" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F6" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="E7" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F7" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="E8" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -18721,7 +19821,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B27" s="75"/>
       <c r="C27" s="75"/>
@@ -18730,39 +19830,39 @@
     </row>
     <row r="28" spans="1:11">
       <c r="B28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F28" t="s">
         <v>1168</v>
       </c>
-      <c r="E28" t="s">
+      <c r="I28" t="s">
         <v>1169</v>
       </c>
-      <c r="F28" t="s">
+      <c r="K28" t="s">
         <v>1170</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1171</v>
-      </c>
-      <c r="K28" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="B30" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="B31" s="24" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="B32" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -18777,85 +19877,85 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="16" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="B39" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G39" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="B40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="G40" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="B41" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G41" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="B42" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G42" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="B43" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="G43" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="12" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="B46" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="12" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="B50" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="16" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -18864,98 +19964,98 @@
     <row r="55" spans="1:4">
       <c r="A55" s="16"/>
       <c r="B55" s="16" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="B56" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D56" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D57" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="B58" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D58" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="B59" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D59" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="B60" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="D60" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="B61" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="D61" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="B62" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="D62" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="B63" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D63" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="B64" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D64" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="B65" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D65" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="B66" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D66" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -18990,77 +20090,77 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="12" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="B76" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="B77" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="B79" s="12" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="C80" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="C82" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="83" spans="2:4">
       <c r="C83" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="C85" s="12" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="D86" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="87" spans="2:4">
       <c r="D87" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="89" spans="2:4">
       <c r="B89" s="12" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="90" spans="2:4">
       <c r="C90" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="D91" s="12" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="D92" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="94" spans="2:4">
       <c r="C94" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -19070,56 +20170,56 @@
     </row>
     <row r="96" spans="2:4">
       <c r="D96" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="B98" s="12" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="C99" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="C100" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="C101" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="16" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="B105" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D105" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="B106" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D106" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="B107" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D107" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -19305,7 +20405,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="2:10">
       <c r="B17" s="16" t="s">
         <v>775</v>
       </c>
@@ -19326,17 +20426,9 @@
         <v>759</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1106</v>
-      </c>
+    <row r="21" spans="2:10">
       <c r="E21" s="53"/>
-      <c r="F21" s="53">
-        <v>46044</v>
-      </c>
+      <c r="F21" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19350,7 +20442,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="16" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -19358,10 +20450,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="16" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F3" s="16"/>
       <c r="H3" s="16" t="s">
@@ -19373,10 +20465,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H4" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -19384,10 +20476,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="H5" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -19412,19 +20504,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="16" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="16"/>
       <c r="B101" s="94" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="16"/>
       <c r="B102" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -19435,7 +20527,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="93" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -19443,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -19451,7 +20543,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -19459,66 +20551,66 @@
         <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="16" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="16"/>
       <c r="B111" s="16" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F111" s="16" t="s">
         <v>1259</v>
-      </c>
-      <c r="F111" s="16" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="16"/>
       <c r="C112" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G112" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="16"/>
       <c r="C113" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="G113" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="16"/>
       <c r="C114" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G114" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="16"/>
       <c r="C115" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G115" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="16"/>
       <c r="C116" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G116" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -19527,7 +20619,7 @@
     <row r="118" spans="1:7">
       <c r="A118" s="16"/>
       <c r="C118" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -19538,7 +20630,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="16" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -19546,131 +20638,131 @@
     </row>
     <row r="123" spans="1:7">
       <c r="B123" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="B124" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="B125" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="B126" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="B128" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="C129" s="22" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="16" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="B132" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="B133" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="B134" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="B135" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="B136" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="B138" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="B140" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="C141" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="G141" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="C142" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G142" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="C143" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="G143" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="145" spans="2:3">
       <c r="B145" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="147" spans="2:3">
       <c r="B147" s="22" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="16" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="150" spans="2:3">
       <c r="C150" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="151" spans="2:3">
       <c r="C151" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="152" spans="2:3">
       <c r="C152" s="22" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="154" spans="2:3">
       <c r="C154" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,13 +17,14 @@
     <sheet name="Свършени задачи" sheetId="9" r:id="rId8"/>
     <sheet name="Задачи" sheetId="10" r:id="rId9"/>
     <sheet name="Инвестиции" sheetId="11" r:id="rId10"/>
+    <sheet name="Родословно дърво" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="1467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1507">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7042,18 +7043,146 @@
   </si>
   <si>
     <t>100+ клекове;</t>
+  </si>
+  <si>
+    <t>Иванка</t>
+  </si>
+  <si>
+    <t>Васил</t>
+  </si>
+  <si>
+    <t>Асен</t>
+  </si>
+  <si>
+    <t>Марийка</t>
+  </si>
+  <si>
+    <t>Сандо</t>
+  </si>
+  <si>
+    <t>Сергия</t>
+  </si>
+  <si>
+    <t>Сашо</t>
+  </si>
+  <si>
+    <t>Росица</t>
+  </si>
+  <si>
+    <t>Надка</t>
+  </si>
+  <si>
+    <t>Родата на баща ми</t>
+  </si>
+  <si>
+    <t>Родата на майка ми</t>
+  </si>
+  <si>
+    <t>Янко</t>
+  </si>
+  <si>
+    <t>Живка</t>
+  </si>
+  <si>
+    <t>Богомил</t>
+  </si>
+  <si>
+    <t>Яне</t>
+  </si>
+  <si>
+    <t>Станка</t>
+  </si>
+  <si>
+    <t>Верка</t>
+  </si>
+  <si>
+    <t>Да питам вуйчо</t>
+  </si>
+  <si>
+    <t>Баба Живка</t>
+  </si>
+  <si>
+    <t>Погребана на:</t>
+  </si>
+  <si>
+    <t>Родена на:</t>
+  </si>
+  <si>
+    <t>Почина на 79:</t>
+  </si>
+  <si>
+    <t>Минали са дни:</t>
+  </si>
+  <si>
+    <t>Минали са години:</t>
+  </si>
+  <si>
+    <t>Тук използваме DATEDIF() funcrion</t>
+  </si>
+  <si>
+    <t>Syntax</t>
+  </si>
+  <si>
+    <t>DATEDIF(first_date, second_date, type_returned_diff)</t>
+  </si>
+  <si>
+    <t>Y - year</t>
+  </si>
+  <si>
+    <t>type_returned_diff</t>
+  </si>
+  <si>
+    <t>YM - months</t>
+  </si>
+  <si>
+    <t>MD - days</t>
+  </si>
+  <si>
+    <t>Функцията изчислява години, месеци и дни като разлика между две дати</t>
+  </si>
+  <si>
+    <t>Как аз да се запозная с повече хора като Стефан Янков</t>
+  </si>
+  <si>
+    <t>Кога не съм сериозен?</t>
+  </si>
+  <si>
+    <t>Защо днес изпих 2 кафета?</t>
+  </si>
+  <si>
+    <t>Защото вчера довърших таблото и го използвах като награда</t>
+  </si>
+  <si>
+    <t>изкуствен интелект, за идеи за готвене, пресмятане на калории</t>
+  </si>
+  <si>
+    <t>събиране на информация за хранене и трениране</t>
+  </si>
+  <si>
+    <t>дисциплина за готвене</t>
+  </si>
+  <si>
+    <t>дисциплина за хранене</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7269,7 +7398,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7285,6 +7414,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7470,7 +7611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7487,93 +7628,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -7588,10 +7729,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10681,6 +10828,105 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>293496</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>48091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>295084</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168959</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1970690" y="2774731"/>
+          <a:ext cx="304800" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>293496</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>48091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>295084</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>168959</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1970690" y="2774731"/>
+          <a:ext cx="304800" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -13942,9 +14188,214 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:J48"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" s="16" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="97" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="C6" s="24" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G6" s="97" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="D9" s="97" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="24" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="16" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18" s="97" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D18" s="97" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F18" s="98" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H18" s="97" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="C21" s="97" t="s">
+        <v>1479</v>
+      </c>
+      <c r="G21" s="97" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="D24" s="24" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="D27" s="24" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="16" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="B31" s="48" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="43" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="43" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="B32" s="4"/>
+      <c r="C32" s="99">
+        <v>16507</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="102">
+        <v>45554</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="99">
+        <v>45556</v>
+      </c>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="F33" s="53"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="48" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="E35" s="48" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="4"/>
+      <c r="C36" s="101">
+        <f ca="1">TODAY()-F32</f>
+        <v>608</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="100" t="str">
+        <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
+        <v>1 години, 8 месеца, 1 дни</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="16" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="C43" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="C45" s="16" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="D46" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="D47" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="D48" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M277"/>
+  <dimension ref="A2:M289"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
@@ -14910,7 +15361,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:3">
       <c r="B113">
         <v>9</v>
       </c>
@@ -14918,7 +15369,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:3">
       <c r="B114">
         <v>10</v>
       </c>
@@ -14926,7 +15377,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:3">
       <c r="B115">
         <v>11</v>
       </c>
@@ -14934,910 +15385,958 @@
         <v>825</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:3">
       <c r="A118" s="16" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:3">
       <c r="A119" s="16"/>
       <c r="B119" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:3">
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>636</v>
-      </c>
-      <c r="G121">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="B123">
         <v>2</v>
       </c>
-      <c r="H121" s="16" t="s">
+      <c r="C123" s="16" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
-      <c r="B128">
+    <row r="125" spans="1:3">
+      <c r="B125">
         <v>3</v>
       </c>
-      <c r="C128" s="16" t="s">
+      <c r="C125" s="16" t="s">
         <v>632</v>
       </c>
-      <c r="G128">
+    </row>
+    <row r="126" spans="1:3">
+      <c r="C126" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="C127" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="B129">
         <v>4</v>
       </c>
-      <c r="H128" s="16" t="s">
+      <c r="C129" s="16" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
-      <c r="C129" t="s">
-        <v>650</v>
-      </c>
-      <c r="H129" t="s">
+    <row r="130" spans="2:3">
+      <c r="C130" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
-      <c r="C130" t="s">
+    <row r="131" spans="2:3">
+      <c r="C131" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="C132" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="C133" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="C134" t="s">
         <v>647</v>
       </c>
-      <c r="H130" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="H131" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="H132" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="H133" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="B138">
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136">
         <v>5</v>
       </c>
-      <c r="C138" s="16" t="s">
+      <c r="C136" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="G138">
+    </row>
+    <row r="137" spans="2:3">
+      <c r="C137" s="61" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3">
+      <c r="B139">
         <v>6</v>
       </c>
-      <c r="H138" s="16" t="s">
+      <c r="C139" s="16" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
-      <c r="C139" s="61" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="16" t="s">
+    <row r="140" spans="2:3">
+      <c r="C140" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3">
+      <c r="C141" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3">
+      <c r="C142" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3">
+      <c r="C143" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3">
+      <c r="C144" s="61"/>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="16" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
-      <c r="B143">
+    <row r="147" spans="1:3">
+      <c r="B147">
         <v>1</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C147" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
-      <c r="B144">
+    <row r="148" spans="1:3">
+      <c r="B148">
         <v>2</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C148" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145">
+    <row r="149" spans="1:3">
+      <c r="B149">
         <v>3</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C149" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="16" t="s">
+    <row r="153" spans="1:3">
+      <c r="A153" s="16" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="B154" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="C155" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="16" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="16" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="16" t="s">
         <v>704</v>
       </c>
-      <c r="F149" s="16" t="s">
+      <c r="F161" s="16" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
-      <c r="B150" t="s">
+    <row r="162" spans="2:6">
+      <c r="B162" t="s">
         <v>703</v>
       </c>
-      <c r="F150" t="s">
+      <c r="F162" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
-      <c r="B151" t="s">
+    <row r="163" spans="2:6">
+      <c r="B163" t="s">
         <v>722</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F163" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" t="s">
         <v>723</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F164" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" t="s">
+    <row r="165" spans="2:6">
+      <c r="B165" t="s">
         <v>725</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F165" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
-      <c r="B154" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" t="s">
         <v>727</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F166" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
-      <c r="B155" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" t="s">
         <v>729</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F167" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
-      <c r="B157" s="16" t="s">
+    <row r="169" spans="2:6">
+      <c r="B169" s="16" t="s">
         <v>707</v>
       </c>
-      <c r="F157" s="16" t="s">
+      <c r="F169" s="16" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
-      <c r="B158" t="s">
+    <row r="170" spans="2:6">
+      <c r="B170" t="s">
         <v>708</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F170" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
-      <c r="B159" t="s">
+    <row r="171" spans="2:6">
+      <c r="B171" t="s">
         <v>709</v>
       </c>
-      <c r="F159" t="s">
+      <c r="F171" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
-      <c r="B160" t="s">
+    <row r="172" spans="2:6">
+      <c r="B172" t="s">
         <v>710</v>
       </c>
-      <c r="F160" t="s">
+      <c r="F172" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
-      <c r="B161" t="s">
+    <row r="173" spans="2:6">
+      <c r="B173" t="s">
         <v>711</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F173" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
-      <c r="B162" t="s">
+    <row r="174" spans="2:6">
+      <c r="B174" t="s">
         <v>793</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F174" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
-      <c r="B163" t="s">
+    <row r="175" spans="2:6">
+      <c r="B175" t="s">
         <v>712</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F175" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
-      <c r="B164" t="s">
+    <row r="176" spans="2:6">
+      <c r="B176" t="s">
         <v>713</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F176" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
-      <c r="B165" t="s">
+    <row r="177" spans="1:12">
+      <c r="B177" t="s">
         <v>714</v>
       </c>
-      <c r="F165" t="s">
+      <c r="F177" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
-      <c r="B166" t="s">
+    <row r="178" spans="1:12">
+      <c r="B178" t="s">
         <v>809</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F178" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
-      <c r="A169" s="16" t="s">
+    <row r="181" spans="1:12">
+      <c r="A181" s="16" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
-      <c r="B171" s="67" t="s">
+    <row r="183" spans="1:12">
+      <c r="B183" s="67" t="s">
         <v>801</v>
       </c>
-      <c r="C171" s="35"/>
-      <c r="D171" s="35"/>
-      <c r="E171" s="34"/>
-      <c r="F171" s="68" t="s">
+      <c r="C183" s="35"/>
+      <c r="D183" s="35"/>
+      <c r="E183" s="34"/>
+      <c r="F183" s="68" t="s">
         <v>802</v>
       </c>
-      <c r="G171" s="35"/>
-      <c r="H171" s="34"/>
-      <c r="I171" s="65" t="s">
+      <c r="G183" s="35"/>
+      <c r="H183" s="34"/>
+      <c r="I183" s="65" t="s">
         <v>808</v>
       </c>
-      <c r="J171" s="35"/>
-      <c r="K171" s="35"/>
-      <c r="L171" s="34"/>
-    </row>
-    <row r="172" spans="1:12">
-      <c r="B172" s="67" t="s">
+      <c r="J183" s="35"/>
+      <c r="K183" s="35"/>
+      <c r="L183" s="34"/>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="B184" s="67" t="s">
         <v>806</v>
       </c>
-      <c r="C172" s="35"/>
-      <c r="D172" s="35"/>
-      <c r="E172" s="34"/>
-      <c r="F172" s="35" t="s">
+      <c r="C184" s="35"/>
+      <c r="D184" s="35"/>
+      <c r="E184" s="34"/>
+      <c r="F184" s="35" t="s">
         <v>820</v>
       </c>
-      <c r="G172" s="35"/>
-      <c r="H172" s="34"/>
-      <c r="I172" s="39"/>
-      <c r="J172" s="35"/>
-      <c r="K172" s="35"/>
-      <c r="L172" s="34"/>
-    </row>
-    <row r="173" spans="1:12">
-      <c r="B173" s="67" t="s">
+      <c r="G184" s="35"/>
+      <c r="H184" s="34"/>
+      <c r="I184" s="39"/>
+      <c r="J184" s="35"/>
+      <c r="K184" s="35"/>
+      <c r="L184" s="34"/>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="B185" s="67" t="s">
         <v>804</v>
       </c>
-      <c r="C173" s="35"/>
-      <c r="D173" s="35"/>
-      <c r="E173" s="34"/>
-      <c r="F173" s="35" t="s">
+      <c r="C185" s="35"/>
+      <c r="D185" s="35"/>
+      <c r="E185" s="34"/>
+      <c r="F185" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="G173" s="35"/>
-      <c r="H173" s="34"/>
-      <c r="I173" s="67" t="s">
+      <c r="G185" s="35"/>
+      <c r="H185" s="34"/>
+      <c r="I185" s="67" t="s">
         <v>805</v>
       </c>
-      <c r="J173" s="35"/>
-      <c r="K173" s="35"/>
-      <c r="L173" s="34"/>
-    </row>
-    <row r="174" spans="1:12">
-      <c r="B174" s="67" t="s">
+      <c r="J185" s="35"/>
+      <c r="K185" s="35"/>
+      <c r="L185" s="34"/>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="B186" s="67" t="s">
         <v>803</v>
       </c>
-      <c r="C174" s="35"/>
-      <c r="D174" s="35"/>
-      <c r="E174" s="34"/>
-      <c r="F174" s="35">
+      <c r="C186" s="35"/>
+      <c r="D186" s="35"/>
+      <c r="E186" s="34"/>
+      <c r="F186" s="35">
         <v>2</v>
       </c>
-      <c r="G174" s="35"/>
-      <c r="H174" s="34"/>
-      <c r="I174" s="39" t="s">
+      <c r="G186" s="35"/>
+      <c r="H186" s="34"/>
+      <c r="I186" s="39" t="s">
         <v>807</v>
       </c>
-      <c r="J174" s="35"/>
-      <c r="K174" s="35"/>
-      <c r="L174" s="34"/>
-    </row>
-    <row r="175" spans="1:12">
-      <c r="B175" s="66"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
-      <c r="K175" s="7"/>
-      <c r="L175" s="7"/>
-    </row>
-    <row r="176" spans="1:12">
-      <c r="B176" s="16"/>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="16" t="s">
+      <c r="J186" s="35"/>
+      <c r="K186" s="35"/>
+      <c r="L186" s="34"/>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="B187" s="66"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="7"/>
+      <c r="K187" s="7"/>
+      <c r="L187" s="7"/>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="B188" s="16"/>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" s="16" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
-      <c r="B179">
+    <row r="191" spans="1:12">
+      <c r="B191">
         <v>1</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C191" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
-      <c r="B180">
+    <row r="192" spans="1:12">
+      <c r="B192">
         <v>2</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C192" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
-      <c r="B181">
+    <row r="193" spans="1:3">
+      <c r="B193">
         <v>3</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C193" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
-      <c r="B182">
+    <row r="194" spans="1:3">
+      <c r="B194">
         <v>4</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C194" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
-      <c r="B183">
+    <row r="195" spans="1:3">
+      <c r="B195">
         <v>5</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C195" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="16" t="s">
+    <row r="198" spans="1:3">
+      <c r="A198" s="16" t="s">
         <v>833</v>
       </c>
-      <c r="B186" s="16"/>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="B188">
+      <c r="B198" s="16"/>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="B200">
         <v>1</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C200" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
-      <c r="B189">
+    <row r="201" spans="1:3">
+      <c r="B201">
         <v>2</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C201" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
-      <c r="B190">
+    <row r="202" spans="1:3">
+      <c r="B202">
         <v>3</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C202" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
-      <c r="B191">
+    <row r="203" spans="1:3">
+      <c r="B203">
         <v>4</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C203" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
-      <c r="A194" s="16" t="s">
+    <row r="206" spans="1:3">
+      <c r="A206" s="16" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
-      <c r="B195" t="s">
+    <row r="207" spans="1:3">
+      <c r="B207" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
-      <c r="C196" t="s">
+    <row r="208" spans="1:3">
+      <c r="C208" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
-      <c r="C197" t="s">
+    <row r="209" spans="1:11">
+      <c r="C209" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
-      <c r="A200" s="16" t="s">
+    <row r="212" spans="1:11">
+      <c r="A212" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
-      <c r="B201" t="s">
+    <row r="213" spans="1:11">
+      <c r="B213" t="s">
         <v>1279</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
-      <c r="B202" s="16" t="s">
+    <row r="214" spans="1:11">
+      <c r="B214" s="16" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
-      <c r="B203" s="95"/>
-    </row>
-    <row r="204" spans="1:11">
-      <c r="B204" s="48" t="s">
+    <row r="215" spans="1:11">
+      <c r="B215" s="95"/>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="B216" s="48" t="s">
         <v>1212</v>
       </c>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="6"/>
-      <c r="G204" s="48" t="s">
+      <c r="C216" s="5"/>
+      <c r="D216" s="5"/>
+      <c r="E216" s="6"/>
+      <c r="G216" s="48" t="s">
         <v>1213</v>
       </c>
-      <c r="H204" s="5"/>
-      <c r="I204" s="5"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="7"/>
-    </row>
-    <row r="205" spans="1:11">
-      <c r="B205" s="3" t="s">
+      <c r="H216" s="5"/>
+      <c r="I216" s="5"/>
+      <c r="J216" s="6"/>
+      <c r="K216" s="7"/>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="B217" s="3" t="s">
         <v>1276</v>
-      </c>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="8"/>
-      <c r="F205" t="s">
-        <v>134</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>1276</v>
-      </c>
-      <c r="H205" s="7"/>
-      <c r="I205" s="7"/>
-      <c r="J205" s="8"/>
-      <c r="K205" s="7"/>
-    </row>
-    <row r="206" spans="1:11">
-      <c r="B206" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="8"/>
-      <c r="F206" t="s">
-        <v>134</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>1277</v>
-      </c>
-      <c r="H206" s="7"/>
-      <c r="I206" s="7"/>
-      <c r="J206" s="8"/>
-      <c r="K206" s="7"/>
-    </row>
-    <row r="207" spans="1:11">
-      <c r="B207" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C207" s="7"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="8"/>
-      <c r="G207" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H207" s="7"/>
-      <c r="I207" s="7"/>
-      <c r="J207" s="8"/>
-      <c r="K207" s="7"/>
-    </row>
-    <row r="208" spans="1:11">
-      <c r="B208" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="8"/>
-      <c r="G208" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H208" s="7"/>
-      <c r="I208" s="7"/>
-      <c r="J208" s="8"/>
-      <c r="K208" s="7"/>
-    </row>
-    <row r="209" spans="2:11">
-      <c r="B209" s="3"/>
-      <c r="C209" s="7"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="8"/>
-      <c r="G209" s="3"/>
-      <c r="H209" s="7"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="8"/>
-      <c r="K209" s="7"/>
-    </row>
-    <row r="210" spans="2:11">
-      <c r="B210" s="3" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C210" s="7"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="8"/>
-      <c r="G210" s="3" t="s">
-        <v>1286</v>
-      </c>
-      <c r="H210" s="7"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="8"/>
-      <c r="K210" s="7"/>
-    </row>
-    <row r="211" spans="2:11">
-      <c r="B211" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C211" s="7"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="8"/>
-      <c r="G211" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="H211" s="7"/>
-      <c r="I211" s="7"/>
-      <c r="J211" s="8"/>
-      <c r="K211" s="7"/>
-    </row>
-    <row r="212" spans="2:11">
-      <c r="B212" s="4" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C212" s="10"/>
-      <c r="D212" s="10"/>
-      <c r="E212" s="11"/>
-      <c r="G212" s="4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="H212" s="10"/>
-      <c r="I212" s="10"/>
-      <c r="J212" s="11"/>
-      <c r="K212" s="7"/>
-    </row>
-    <row r="214" spans="2:11">
-      <c r="B214" s="48" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="6"/>
-    </row>
-    <row r="215" spans="2:11">
-      <c r="B215" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C215" s="7"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="8"/>
-    </row>
-    <row r="216" spans="2:11">
-      <c r="B216" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C216" s="7"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="8"/>
-    </row>
-    <row r="217" spans="2:11">
-      <c r="B217" s="3" t="s">
-        <v>1289</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
       <c r="E217" s="8"/>
-    </row>
-    <row r="218" spans="2:11">
+      <c r="F217" t="s">
+        <v>134</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H217" s="7"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="8"/>
+      <c r="K217" s="7"/>
+    </row>
+    <row r="218" spans="1:11">
       <c r="B218" s="3" t="s">
-        <v>1278</v>
+        <v>1292</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
       <c r="E218" s="8"/>
-    </row>
-    <row r="219" spans="2:11">
-      <c r="B219" s="3"/>
+      <c r="F218" t="s">
+        <v>134</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H218" s="7"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="7"/>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="B219" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="8"/>
-    </row>
-    <row r="220" spans="2:11">
+      <c r="G219" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H219" s="7"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="7"/>
+    </row>
+    <row r="220" spans="1:11">
       <c r="B220" s="3" t="s">
-        <v>1293</v>
+        <v>1278</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="8"/>
-    </row>
-    <row r="221" spans="2:11">
-      <c r="B221" s="3" t="s">
-        <v>1294</v>
-      </c>
+      <c r="G220" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H220" s="7"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="7"/>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="B221" s="3"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="8"/>
-    </row>
-    <row r="222" spans="2:11">
-      <c r="B222" s="4" t="s">
+      <c r="G221" s="3"/>
+      <c r="H221" s="7"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="7"/>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="B222" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7"/>
+      <c r="E222" s="8"/>
+      <c r="G222" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H222" s="7"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="8"/>
+      <c r="K222" s="7"/>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="B223" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="8"/>
+      <c r="G223" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H223" s="7"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="8"/>
+      <c r="K223" s="7"/>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="B224" s="4" t="s">
         <v>1283</v>
       </c>
-      <c r="C222" s="10"/>
-      <c r="D222" s="10"/>
-      <c r="E222" s="11"/>
-    </row>
-    <row r="225" spans="1:4">
-      <c r="A225" s="16" t="s">
+      <c r="C224" s="10"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="11"/>
+      <c r="G224" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H224" s="10"/>
+      <c r="I224" s="10"/>
+      <c r="J224" s="11"/>
+      <c r="K224" s="7"/>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="B226" s="48" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C226" s="5"/>
+      <c r="D226" s="5"/>
+      <c r="E226" s="6"/>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="B227" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C227" s="7"/>
+      <c r="D227" s="7"/>
+      <c r="E227" s="8"/>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="B228" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7"/>
+      <c r="E228" s="8"/>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="B229" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C229" s="7"/>
+      <c r="D229" s="7"/>
+      <c r="E229" s="8"/>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="B230" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C230" s="7"/>
+      <c r="D230" s="7"/>
+      <c r="E230" s="8"/>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="B231" s="3"/>
+      <c r="C231" s="7"/>
+      <c r="D231" s="7"/>
+      <c r="E231" s="8"/>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="B232" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7"/>
+      <c r="E232" s="8"/>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="B233" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7"/>
+      <c r="E233" s="8"/>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="B234" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C234" s="10"/>
+      <c r="D234" s="10"/>
+      <c r="E234" s="11"/>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="16" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
-      <c r="B226" s="16" t="s">
+    <row r="238" spans="1:5">
+      <c r="B238" s="16" t="s">
         <v>1304</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
-      <c r="C228" s="16" t="s">
+    <row r="240" spans="1:5">
+      <c r="C240" s="16" t="s">
         <v>1296</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
-      <c r="D229" t="s">
+    <row r="241" spans="2:4">
+      <c r="D241" t="s">
         <v>1297</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
-      <c r="D230" t="s">
+    <row r="242" spans="2:4">
+      <c r="D242" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
-      <c r="D231" t="s">
+    <row r="243" spans="2:4">
+      <c r="D243" t="s">
         <v>1299</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
-      <c r="D232" t="s">
+    <row r="244" spans="2:4">
+      <c r="D244" t="s">
         <v>1300</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
-      <c r="D233" t="s">
+    <row r="245" spans="2:4">
+      <c r="D245" t="s">
         <v>1301</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
-      <c r="D234" t="s">
+    <row r="246" spans="2:4">
+      <c r="D246" t="s">
         <v>1302</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
-      <c r="C236" s="16" t="s">
+    <row r="248" spans="2:4">
+      <c r="C248" s="16" t="s">
         <v>1306</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
-      <c r="D237" t="s">
+    <row r="249" spans="2:4">
+      <c r="D249" t="s">
         <v>1303</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
-      <c r="D238" t="s">
+    <row r="250" spans="2:4">
+      <c r="D250" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
-      <c r="B240" t="s">
+    <row r="252" spans="2:4">
+      <c r="B252" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
-      <c r="C242" s="16" t="s">
+    <row r="254" spans="2:4">
+      <c r="C254" s="16" t="s">
         <v>1296</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
-      <c r="D243" t="s">
+    <row r="255" spans="2:4">
+      <c r="D255" t="s">
         <v>1308</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
-      <c r="D244" t="s">
+    <row r="256" spans="2:4">
+      <c r="D256" t="s">
         <v>1309</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
-      <c r="D245" t="s">
+    <row r="257" spans="1:4">
+      <c r="D257" t="s">
         <v>1310</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
-      <c r="D246" t="s">
+    <row r="258" spans="1:4">
+      <c r="D258" t="s">
         <v>1311</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
-      <c r="D247" t="s">
+    <row r="259" spans="1:4">
+      <c r="D259" t="s">
         <v>1312</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
-      <c r="C249" s="16" t="s">
+    <row r="261" spans="1:4">
+      <c r="C261" s="16" t="s">
         <v>1306</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
-      <c r="D250" t="s">
+    <row r="262" spans="1:4">
+      <c r="D262" t="s">
         <v>1313</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
-      <c r="D251" t="s">
+    <row r="263" spans="1:4">
+      <c r="D263" t="s">
         <v>1314</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
-      <c r="D252" t="s">
+    <row r="264" spans="1:4">
+      <c r="D264" t="s">
         <v>1315</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
-      <c r="D253" t="s">
+    <row r="265" spans="1:4">
+      <c r="D265" t="s">
         <v>1316</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
-      <c r="A256" s="16" t="s">
+    <row r="268" spans="1:4">
+      <c r="A268" s="16" t="s">
         <v>1317</v>
       </c>
     </row>
-    <row r="258" spans="2:2">
-      <c r="B258" t="s">
+    <row r="270" spans="1:4">
+      <c r="B270" t="s">
         <v>1318</v>
       </c>
     </row>
-    <row r="259" spans="2:2">
-      <c r="B259" t="s">
+    <row r="271" spans="1:4">
+      <c r="B271" t="s">
         <v>1327</v>
       </c>
     </row>
-    <row r="260" spans="2:2">
-      <c r="B260" t="s">
+    <row r="272" spans="1:4">
+      <c r="B272" t="s">
         <v>1319</v>
-      </c>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="264" spans="2:2">
-      <c r="B264" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="265" spans="2:2">
-      <c r="B265" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="266" spans="2:2">
-      <c r="B266" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2">
-      <c r="B268" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="269" spans="2:2">
-      <c r="B269" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="270" spans="2:2">
-      <c r="B270" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="271" spans="2:2">
-      <c r="B271" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="272" spans="2:2">
-      <c r="B272" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>1331</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" t="s">
         <v>1332</v>
       </c>
     </row>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1538">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7163,6 +7163,125 @@
   </si>
   <si>
     <t>дисциплина за хранене</t>
+  </si>
+  <si>
+    <t>спокойствието на водата</t>
+  </si>
+  <si>
+    <t>емоциите</t>
+  </si>
+  <si>
+    <t>Ако водата е спокойна - значи си в равновесие</t>
+  </si>
+  <si>
+    <t>ръцете, които държат съда</t>
+  </si>
+  <si>
+    <t>мислите</t>
+  </si>
+  <si>
+    <t>Ако мислите ти са положителни - емоциите са спокойни</t>
+  </si>
+  <si>
+    <t>цвета на стъклото на съда</t>
+  </si>
+  <si>
+    <t>подсъзнание и вярвания</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ако вярванията ти са положителни - цвета е хубав и съда изглежда добре. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Това влияе на действията ти</t>
+    </r>
+  </si>
+  <si>
+    <t>дебелината/здравината на съда</t>
+  </si>
+  <si>
+    <t>сила на духа и характер</t>
+  </si>
+  <si>
+    <t>Ако си силен физически и ментално дебелината на съда е здрава</t>
+  </si>
+  <si>
+    <t>красиви цветове и форми на съда</t>
+  </si>
+  <si>
+    <t>действия и навици</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ако действията ти са добри, стените на съда се оцветяват в красиви цветове - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>това е реалнията ти живот</t>
+    </r>
+  </si>
+  <si>
+    <t>формата на съда</t>
+  </si>
+  <si>
+    <t>тялото</t>
+  </si>
+  <si>
+    <t>Ако тренираш, съда ще има красива форма</t>
+  </si>
+  <si>
+    <t>Бистротата на водата</t>
+  </si>
+  <si>
+    <t>щастие и вътрешна чистота</t>
+  </si>
+  <si>
+    <t>Ако си щастлив, водата ще бъде чиста, бистра</t>
+  </si>
+  <si>
+    <t>Количеството на водата</t>
+  </si>
+  <si>
+    <t>Жизнената енергия</t>
+  </si>
+  <si>
+    <t>Ако имаш енергия, мотиовация, сили за действие - водата е много</t>
+  </si>
+  <si>
+    <t>Големината на съда</t>
+  </si>
+  <si>
+    <t>Съзнанието / нивото на осъзнатост</t>
+  </si>
+  <si>
+    <t>Колкото по-широко е съзнанието ти, толкова повече от живота можеш да побереш и разбереш.</t>
+  </si>
+  <si>
+    <t>Човешки живот - съд с вода</t>
+  </si>
+  <si>
+    <t>Ти</t>
+  </si>
+  <si>
+    <t>Ти си осъзнатостта която наблюдава съда, не си чувствата, не си мислите</t>
+  </si>
+  <si>
+    <t>осъзнатост</t>
   </si>
 </sst>
 </file>
@@ -14336,12 +14455,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="101">
         <f ca="1">TODAY()-F32</f>
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="100" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 8 месеца, 1 дни</v>
+        <v>1 години, 8 месеца, 15 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -20178,7 +20297,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A5:K107"/>
+  <dimension ref="A5:K121"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
@@ -20672,32 +20791,32 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:9">
       <c r="B98" s="12" t="s">
         <v>1187</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:9">
       <c r="C99" t="s">
         <v>1188</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:9">
       <c r="C100" t="s">
         <v>1189</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:9">
       <c r="C101" t="s">
         <v>1190</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:9">
       <c r="A104" s="16" t="s">
         <v>1266</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:9">
       <c r="B105" t="s">
         <v>1267</v>
       </c>
@@ -20705,7 +20824,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:9">
       <c r="B106" t="s">
         <v>1269</v>
       </c>
@@ -20713,12 +20832,160 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:9">
       <c r="B107" t="s">
         <v>1271</v>
       </c>
       <c r="D107" t="s">
         <v>1270</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="16" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="16"/>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9">
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9">
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I114" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9">
+      <c r="B115">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I115" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9">
+      <c r="B116">
+        <v>4</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1517</v>
+      </c>
+      <c r="I116" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9">
+      <c r="B117">
+        <v>5</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I117" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9">
+      <c r="B118">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1523</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9">
+      <c r="B119">
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I119" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9">
+      <c r="B120">
+        <v>8</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9">
+      <c r="B121">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1532</v>
+      </c>
+      <c r="I121" t="s">
+        <v>1533</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="Задачи" sheetId="10" r:id="rId9"/>
     <sheet name="Инвестиции" sheetId="11" r:id="rId10"/>
     <sheet name="Родословно дърво" sheetId="12" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1560">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7282,6 +7283,72 @@
   </si>
   <si>
     <t>осъзнатост</t>
+  </si>
+  <si>
+    <t>As a man thinketh by James Alien</t>
+  </si>
+  <si>
+    <t>Мислиш, ствараш</t>
+  </si>
+  <si>
+    <t>Мисли и действай всеки ден</t>
+  </si>
+  <si>
+    <t>Мисълта е искра</t>
+  </si>
+  <si>
+    <t>Действието е горивото</t>
+  </si>
+  <si>
+    <t>Навика е двигателя</t>
+  </si>
+  <si>
+    <t>Съдбата е дестинацията</t>
+  </si>
+  <si>
+    <t>Аз съм създателя на моя живот</t>
+  </si>
+  <si>
+    <t>Мислите ти са семената</t>
+  </si>
+  <si>
+    <t>Обстоятелствата са реколтата</t>
+  </si>
+  <si>
+    <t>Мислите оформят характера(сумата от повторените ти мисли)</t>
+  </si>
+  <si>
+    <t>Мислите ти създават обстоятелствата</t>
+  </si>
+  <si>
+    <t>Целта направлява мислите. Всяка сутрин си задай въпроса "каква е целта ми за днес"</t>
+  </si>
+  <si>
+    <t>Самоконтрола изгражда сила и това се случва когато човек започне да контролира мислите си.</t>
+  </si>
+  <si>
+    <t>Спокойствието е най-висша форма на майсторство</t>
+  </si>
+  <si>
+    <t>Следи мислите си</t>
+  </si>
+  <si>
+    <t>Избери идеалите си и приравни мислите си спрямо тях</t>
+  </si>
+  <si>
+    <t>Визуализирай с цел</t>
+  </si>
+  <si>
+    <t>не реагирай, а отговаряй</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Семената са ръцети те, почвата е в ума ти, реколтата е твоето бъдеще </t>
+  </si>
+  <si>
+    <t>Какъв живот създавам с мислите които имам днес?</t>
+  </si>
+  <si>
+    <t>Atomic habits</t>
   </si>
 </sst>
 </file>
@@ -14455,12 +14522,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="101">
         <f ca="1">TODAY()-F32</f>
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="100" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 8 месеца, 15 дни</v>
+        <v>1 години, 8 месеца, 19 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -14509,6 +14576,126 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:B31"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" s="16" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" s="94" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" s="94" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="11"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,17 +15,17 @@
     <sheet name="Електро цени" sheetId="6" r:id="rId6"/>
     <sheet name="Diagram" sheetId="7" r:id="rId7"/>
     <sheet name="Свършени задачи" sheetId="9" r:id="rId8"/>
-    <sheet name="Задачи" sheetId="10" r:id="rId9"/>
+    <sheet name="Седмица" sheetId="10" r:id="rId9"/>
     <sheet name="Инвестиции" sheetId="11" r:id="rId10"/>
     <sheet name="Родословно дърво" sheetId="12" r:id="rId11"/>
-    <sheet name="Sheet2" sheetId="13" r:id="rId12"/>
+    <sheet name="Книги" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1575">
   <si>
     <t>Мисъл</t>
   </si>
@@ -5675,21 +5675,6 @@
     <t>€</t>
   </si>
   <si>
-    <t>Предстоящи задачи</t>
-  </si>
-  <si>
-    <t>Кога</t>
-  </si>
-  <si>
-    <t>Вид задача</t>
-  </si>
-  <si>
-    <t>Гуми</t>
-  </si>
-  <si>
-    <t>Проучване-цени и марки</t>
-  </si>
-  <si>
     <t>Начална дата: 18,01,2026г</t>
   </si>
   <si>
@@ -5735,12 +5720,6 @@
     <t>Паролатя е ясна - начертаване на фигурата</t>
   </si>
   <si>
-    <t>Накладки + лагер/ Геле</t>
-  </si>
-  <si>
-    <t>Уточняване на дата</t>
-  </si>
-  <si>
     <t>Sad</t>
   </si>
   <si>
@@ -7097,9 +7076,6 @@
     <t>Верка</t>
   </si>
   <si>
-    <t>Да питам вуйчо</t>
-  </si>
-  <si>
     <t>Баба Живка</t>
   </si>
   <si>
@@ -7349,13 +7325,102 @@
   </si>
   <si>
     <t>Atomic habits</t>
+  </si>
+  <si>
+    <t>Методий</t>
+  </si>
+  <si>
+    <t>Понеделник</t>
+  </si>
+  <si>
+    <t>Вторник</t>
+  </si>
+  <si>
+    <t>Сряда</t>
+  </si>
+  <si>
+    <t>Четвъртък</t>
+  </si>
+  <si>
+    <t>Петък</t>
+  </si>
+  <si>
+    <t>Събота</t>
+  </si>
+  <si>
+    <t>Неделя</t>
+  </si>
+  <si>
+    <t>лостове</t>
+  </si>
+  <si>
+    <t>бокс</t>
+  </si>
+  <si>
+    <t>книга</t>
+  </si>
+  <si>
+    <t>под.готв</t>
+  </si>
+  <si>
+    <t>готвене</t>
+  </si>
+  <si>
+    <t>без алкохол</t>
+  </si>
+  <si>
+    <t>1 кафе</t>
+  </si>
+  <si>
+    <t>без порно</t>
+  </si>
+  <si>
+    <t>без маст</t>
+  </si>
+  <si>
+    <t>Вечеря:</t>
+  </si>
+  <si>
+    <t>2 пържоли + картофена салата</t>
+  </si>
+  <si>
+    <t>Следобедна:</t>
+  </si>
+  <si>
+    <t>2 банана + орехи</t>
+  </si>
+  <si>
+    <t>Пазар:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>домати</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, хляб</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7583,6 +7648,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -7797,7 +7870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7920,11 +7993,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14147,23 +14223,23 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="D4" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="86" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -14212,10 +14288,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="B10" s="89" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -14227,10 +14303,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="89" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -14242,10 +14318,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="90" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -14258,7 +14334,7 @@
     <row r="13" spans="1:11">
       <c r="C13" s="62"/>
       <c r="D13" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -14271,7 +14347,7 @@
     <row r="14" spans="1:11">
       <c r="C14" s="62"/>
       <c r="D14" s="3" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -14284,7 +14360,7 @@
     <row r="15" spans="1:11">
       <c r="C15" s="62"/>
       <c r="D15" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -14297,7 +14373,7 @@
     <row r="16" spans="1:11">
       <c r="C16" s="62"/>
       <c r="D16" s="3" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -14310,7 +14386,7 @@
     <row r="17" spans="3:11">
       <c r="C17" s="62"/>
       <c r="D17" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -14323,7 +14399,7 @@
     <row r="18" spans="3:11">
       <c r="C18" s="62"/>
       <c r="D18" s="3" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -14336,7 +14412,7 @@
     <row r="19" spans="3:11">
       <c r="C19" s="62"/>
       <c r="D19" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -14349,7 +14425,7 @@
     <row r="20" spans="3:11">
       <c r="C20" s="62"/>
       <c r="D20" s="4" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -14365,7 +14441,7 @@
     </row>
     <row r="22" spans="3:11">
       <c r="C22" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="G22" s="63"/>
     </row>
@@ -14386,119 +14462,119 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" s="16" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="97" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="D4" s="97" t="s">
-        <v>1470</v>
+        <v>1463</v>
       </c>
       <c r="F4" s="97" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
       <c r="H4" s="97" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="C6" s="24" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="G6" s="97" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" s="97" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="24" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="16" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" s="97" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F18" s="98" t="s">
-        <v>1484</v>
+        <v>1475</v>
+      </c>
+      <c r="F18" s="102" t="s">
+        <v>1552</v>
       </c>
       <c r="H18" s="97" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="C21" s="97" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="G21" s="97" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="D24" s="24" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="D27" s="24" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="16" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="B31" s="48" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="43" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="43" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10">
       <c r="B32" s="4"/>
-      <c r="C32" s="99">
+      <c r="C32" s="98">
         <v>16507</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="102">
+      <c r="F32" s="101">
         <v>45554</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="99">
+      <c r="I32" s="98">
         <v>45556</v>
       </c>
       <c r="J32" s="11"/>
@@ -14508,11 +14584,11 @@
     </row>
     <row r="35" spans="2:8">
       <c r="B35" s="48" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="C35" s="6"/>
       <c r="E35" s="48" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -14520,56 +14596,56 @@
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="4"/>
-      <c r="C36" s="101">
+      <c r="C36" s="100">
         <f ca="1">TODAY()-F32</f>
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="E36" s="4"/>
-      <c r="F36" s="100" t="str">
+      <c r="F36" s="99" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 8 месеца, 19 дни</v>
+        <v>1 години, 9 месеца, 3 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="16" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="C43" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="C45" s="16" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="D46" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="D47" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="D48" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
     </row>
   </sheetData>
@@ -14586,112 +14662,112 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="B17" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="B18" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="B19" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="B23" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="B24" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="B25" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="B26" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="94" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="94" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="16" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
     </row>
   </sheetData>
@@ -14831,7 +14907,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="B24" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -15143,7 +15219,7 @@
     </row>
     <row r="56" spans="1:12">
       <c r="C56" s="16" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>598</v>
@@ -15171,7 +15247,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="H58" t="s">
         <v>599</v>
@@ -15329,7 +15405,7 @@
         <v>848</v>
       </c>
       <c r="L69" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="M69" s="63"/>
     </row>
@@ -15707,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -15792,22 +15868,22 @@
     </row>
     <row r="140" spans="2:3">
       <c r="C140" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="141" spans="2:3">
       <c r="C141" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="142" spans="2:3">
       <c r="C142" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="143" spans="2:3">
       <c r="C143" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="144" spans="2:3">
@@ -15844,17 +15920,17 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="16" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="B154" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="C155" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -16203,12 +16279,12 @@
     </row>
     <row r="213" spans="1:11">
       <c r="B213" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="214" spans="1:11">
       <c r="B214" s="16" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -16216,13 +16292,13 @@
     </row>
     <row r="216" spans="1:11">
       <c r="B216" s="48" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
       <c r="E216" s="6"/>
       <c r="G216" s="48" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
@@ -16231,7 +16307,7 @@
     </row>
     <row r="217" spans="1:11">
       <c r="B217" s="3" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -16240,7 +16316,7 @@
         <v>134</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="H217" s="7"/>
       <c r="I217" s="7"/>
@@ -16249,7 +16325,7 @@
     </row>
     <row r="218" spans="1:11">
       <c r="B218" s="3" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -16258,7 +16334,7 @@
         <v>134</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="H218" s="7"/>
       <c r="I218" s="7"/>
@@ -16267,13 +16343,13 @@
     </row>
     <row r="219" spans="1:11">
       <c r="B219" s="3" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="8"/>
       <c r="G219" s="3" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="H219" s="7"/>
       <c r="I219" s="7"/>
@@ -16282,13 +16358,13 @@
     </row>
     <row r="220" spans="1:11">
       <c r="B220" s="3" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="8"/>
       <c r="G220" s="3" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="H220" s="7"/>
       <c r="I220" s="7"/>
@@ -16308,13 +16384,13 @@
     </row>
     <row r="222" spans="1:11">
       <c r="B222" s="3" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
       <c r="E222" s="8"/>
       <c r="G222" s="3" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="H222" s="7"/>
       <c r="I222" s="7"/>
@@ -16323,13 +16399,13 @@
     </row>
     <row r="223" spans="1:11">
       <c r="B223" s="3" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
       <c r="E223" s="8"/>
       <c r="G223" s="3" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="7"/>
@@ -16338,13 +16414,13 @@
     </row>
     <row r="224" spans="1:11">
       <c r="B224" s="4" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="C224" s="10"/>
       <c r="D224" s="10"/>
       <c r="E224" s="11"/>
       <c r="G224" s="4" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="H224" s="10"/>
       <c r="I224" s="10"/>
@@ -16353,7 +16429,7 @@
     </row>
     <row r="226" spans="1:5">
       <c r="B226" s="48" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
@@ -16361,7 +16437,7 @@
     </row>
     <row r="227" spans="1:5">
       <c r="B227" s="3" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -16369,7 +16445,7 @@
     </row>
     <row r="228" spans="1:5">
       <c r="B228" s="3" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -16377,7 +16453,7 @@
     </row>
     <row r="229" spans="1:5">
       <c r="B229" s="3" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -16385,7 +16461,7 @@
     </row>
     <row r="230" spans="1:5">
       <c r="B230" s="3" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -16399,7 +16475,7 @@
     </row>
     <row r="232" spans="1:5">
       <c r="B232" s="3" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -16407,7 +16483,7 @@
     </row>
     <row r="233" spans="1:5">
       <c r="B233" s="3" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -16415,7 +16491,7 @@
     </row>
     <row r="234" spans="1:5">
       <c r="B234" s="4" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="C234" s="10"/>
       <c r="D234" s="10"/>
@@ -16423,227 +16499,227 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="16" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="B238" s="16" t="s">
-        <v>1304</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="C240" s="16" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="241" spans="2:4">
       <c r="D241" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="242" spans="2:4">
       <c r="D242" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="243" spans="2:4">
       <c r="D243" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="244" spans="2:4">
       <c r="D244" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="245" spans="2:4">
       <c r="D245" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="246" spans="2:4">
       <c r="D246" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="248" spans="2:4">
       <c r="C248" s="16" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="249" spans="2:4">
       <c r="D249" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="250" spans="2:4">
       <c r="D250" t="s">
-        <v>1305</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="252" spans="2:4">
       <c r="B252" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="254" spans="2:4">
       <c r="C254" s="16" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="255" spans="2:4">
       <c r="D255" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="256" spans="2:4">
       <c r="D256" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="D257" t="s">
-        <v>1310</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="D258" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="D259" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="C261" s="16" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="D262" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="D263" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="D264" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="D265" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="16" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="B270" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="B271" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="B272" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>1329</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>1330</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -17748,42 +17824,42 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="16" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="B82" s="16" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="C83" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="C84" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="C85" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="C86" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="C87" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="B89" s="16" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -17797,117 +17873,117 @@
         <v>591</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
       <c r="K90" s="16" t="s">
         <v>594</v>
       </c>
       <c r="L90" s="16" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="C91" s="25" t="s">
-        <v>1346</v>
+        <v>1339</v>
       </c>
       <c r="E91" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I91" t="s">
         <v>1351</v>
       </c>
-      <c r="G91" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I91" t="s">
-        <v>1358</v>
-      </c>
       <c r="K91" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="L91" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="C92" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="E92" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I92" t="s">
         <v>1352</v>
       </c>
-      <c r="G92" t="s">
-        <v>1355</v>
-      </c>
-      <c r="I92" t="s">
-        <v>1359</v>
-      </c>
       <c r="K92" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="L92" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="C93" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
       <c r="E93" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
       <c r="G93" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
       <c r="K93" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="C94" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="C95" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="97" spans="2:7">
       <c r="C97" s="16" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="98" spans="2:7">
       <c r="D98" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="99" spans="2:7">
       <c r="D99" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="100" spans="2:7">
       <c r="D100" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="101" spans="2:7">
       <c r="D101" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="102" spans="2:7">
       <c r="D102" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="103" spans="2:7">
       <c r="D103" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="105" spans="2:7">
       <c r="B105" s="16" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="106" spans="2:7">
@@ -17918,7 +17994,7 @@
         <v>591</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>594</v>
@@ -17926,27 +18002,27 @@
     </row>
     <row r="107" spans="2:7">
       <c r="C107" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E107" t="s">
         <v>1373</v>
       </c>
-      <c r="D107" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1380</v>
-      </c>
       <c r="G107" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="108" spans="2:7">
       <c r="C108" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E108" t="s">
         <v>1374</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1381</v>
       </c>
       <c r="G108" t="s">
         <v>789</v>
@@ -17954,133 +18030,133 @@
     </row>
     <row r="109" spans="2:7">
       <c r="C109" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E109" s="25" t="s">
         <v>1375</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E109" s="25" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="110" spans="2:7">
       <c r="C110" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="112" spans="2:7">
       <c r="C112" s="16" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="113" spans="2:4">
       <c r="D113" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="114" spans="2:4">
       <c r="D114" s="25" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="115" spans="2:4">
       <c r="D115" s="25" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="116" spans="2:4">
       <c r="D116" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="117" spans="2:4">
       <c r="D117" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="118" spans="2:4">
       <c r="D118" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="120" spans="2:4">
       <c r="B120" s="16" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="121" spans="2:4">
       <c r="C121" s="16" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="122" spans="2:4">
       <c r="D122" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="124" spans="2:4">
       <c r="C124" s="16" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="125" spans="2:4">
       <c r="D125" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="127" spans="2:4">
       <c r="D127" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="128" spans="2:4">
       <c r="D128" s="25" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="D129" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="D130" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="D131" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="D132" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="D133" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="16" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="C136" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="C137" s="96" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="C139" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="140" spans="2:5">
@@ -18088,73 +18164,73 @@
         <v>790</v>
       </c>
       <c r="E140" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="D141" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="E141" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="D142" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="E142" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="D143" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="16" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="C146" s="16" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="147" spans="2:4">
       <c r="C147" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="C149" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="150" spans="2:4">
       <c r="C150" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="C151" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="C152" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="C153" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="C154" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -18164,162 +18240,162 @@
     </row>
     <row r="157" spans="2:4">
       <c r="D157" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="D158" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="D159" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="D160" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="D161" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="16" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="C164" s="16" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="D165" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="E166" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="167" spans="2:5">
       <c r="E167" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="169" spans="2:5">
       <c r="C169" s="16" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="170" spans="2:5">
       <c r="D170" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="171" spans="2:5">
       <c r="D171" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="172" spans="2:5">
       <c r="D172" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="174" spans="2:5">
       <c r="C174" s="16" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="175" spans="2:5">
       <c r="D175" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="176" spans="2:5">
       <c r="D176" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="177" spans="2:4">
       <c r="D177" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="179" spans="2:4">
       <c r="C179" s="16" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="180" spans="2:4">
       <c r="D180" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="181" spans="2:4">
       <c r="D181" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="182" spans="2:4">
       <c r="D182" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="183" spans="2:4">
       <c r="D183" s="25" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="184" spans="2:4">
       <c r="B184" s="16" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="185" spans="2:4">
       <c r="C185" s="16" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="186" spans="2:4">
       <c r="C186" s="96" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="187" spans="2:4">
       <c r="D187" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="188" spans="2:4">
       <c r="D188" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="189" spans="2:4">
       <c r="D189" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="D190" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="191" spans="2:4">
       <c r="D191" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="192" spans="2:4">
       <c r="D192" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="194" spans="2:4">
@@ -18329,37 +18405,37 @@
     </row>
     <row r="195" spans="2:4">
       <c r="D195" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="196" spans="2:4">
       <c r="D196" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="197" spans="2:4">
       <c r="D197" t="s">
-        <v>1446</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="198" spans="2:4">
       <c r="D198" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="200" spans="2:4">
       <c r="D200" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="202" spans="2:4">
       <c r="B202" s="16" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="204" spans="2:4">
       <c r="C204" s="16" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="205" spans="2:4">
@@ -18369,109 +18445,109 @@
     </row>
     <row r="206" spans="2:4">
       <c r="C206" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="207" spans="2:4">
       <c r="C207" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="208" spans="2:4">
       <c r="C208" t="s">
-        <v>1450</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="209" spans="2:5">
       <c r="C209" t="s">
-        <v>1451</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="210" spans="2:5">
       <c r="C210" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="211" spans="2:5">
       <c r="C211" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="212" spans="2:5">
       <c r="C212" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="213" spans="2:5">
       <c r="C213" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="214" spans="2:5">
       <c r="C214" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="216" spans="2:5">
       <c r="B216" s="16" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="217" spans="2:5">
       <c r="C217" s="16" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="218" spans="2:5">
       <c r="C218" t="s">
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="E218" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="219" spans="2:5">
       <c r="C219" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="E219" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="220" spans="2:5">
       <c r="C220" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="E220" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="222" spans="2:5">
       <c r="B222" s="16" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="223" spans="2:5">
       <c r="C223" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="224" spans="2:5">
       <c r="D224" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="225" spans="4:4">
       <c r="D225" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="226" spans="4:4">
       <c r="D226" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
     </row>
   </sheetData>
@@ -20126,77 +20202,77 @@
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" s="16" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -20496,28 +20572,28 @@
         <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="E6" s="84" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="F6" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="E7" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="F7" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="E8" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -20626,7 +20702,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="B27" s="75"/>
       <c r="C27" s="75"/>
@@ -20635,39 +20711,39 @@
     </row>
     <row r="28" spans="1:11">
       <c r="B28" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="E28" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="F28" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="I28" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="K28" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="B30" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="B31" s="24" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="B32" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -20682,85 +20758,85 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="16" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="B39" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="G39" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="B40" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="G40" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="B41" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="G41" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="B42" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="G42" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="B43" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="G43" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="12" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="B46" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="12" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="B50" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="16" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -20769,98 +20845,98 @@
     <row r="55" spans="1:4">
       <c r="A55" s="16"/>
       <c r="B55" s="16" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="B56" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="D56" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="D57" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="B58" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="D58" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="B59" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="D59" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="B60" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="D60" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="B61" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="D61" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="B62" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="D62" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="B63" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="D63" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="B64" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="D64" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="B65" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="D65" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="B66" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="D66" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -20895,77 +20971,77 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="12" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="B76" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="B77" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="B79" s="12" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="C80" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="C82" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="83" spans="2:4">
       <c r="C83" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="C85" s="12" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="D86" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="87" spans="2:4">
       <c r="D87" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="89" spans="2:4">
       <c r="B89" s="12" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="90" spans="2:4">
       <c r="C90" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="D91" s="12" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="D92" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="94" spans="2:4">
       <c r="C94" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -20975,61 +21051,61 @@
     </row>
     <row r="96" spans="2:4">
       <c r="D96" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="B98" s="12" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="C99" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="C100" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="C101" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="16" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="B105" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="D105" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="B106" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="D106" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="B107" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="D107" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="16" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -21040,13 +21116,13 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="F112" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="I112" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="113" spans="2:9">
@@ -21054,13 +21130,13 @@
         <v>1</v>
       </c>
       <c r="C113" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="F113" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="I113" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="114" spans="2:9">
@@ -21068,13 +21144,13 @@
         <v>2</v>
       </c>
       <c r="C114" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="F114" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="I114" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="115" spans="2:9">
@@ -21082,13 +21158,13 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="F115" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="I115" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="116" spans="2:9">
@@ -21096,13 +21172,13 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="F116" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="I116" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="117" spans="2:9">
@@ -21110,13 +21186,13 @@
         <v>5</v>
       </c>
       <c r="C117" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="F117" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
       <c r="I117" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="118" spans="2:9">
@@ -21124,13 +21200,13 @@
         <v>6</v>
       </c>
       <c r="C118" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="F118" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="I118" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="119" spans="2:9">
@@ -21138,13 +21214,13 @@
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
       <c r="F119" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="I119" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="120" spans="2:9">
@@ -21152,13 +21228,13 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="F120" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="I120" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="121" spans="2:9">
@@ -21166,13 +21242,13 @@
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="F121" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="I121" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
     </row>
   </sheetData>
@@ -21390,332 +21466,568 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="16" t="s">
-        <v>1102</v>
-      </c>
+      <c r="A1" s="16"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="16"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="16" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F3" s="16"/>
-      <c r="H3" s="16" t="s">
-        <v>511</v>
+      <c r="B3" s="52" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>1559</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="24" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="104"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="24" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="24" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>1564</v>
+      </c>
+      <c r="G12" s="24"/>
+      <c r="H12" s="104"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="49" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" s="24" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="49" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="105" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="49" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="24" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="24" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="24" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="24" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="24" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="16" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="16"/>
+      <c r="B110" s="94" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="16"/>
+      <c r="B111" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="16"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>1105</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
+      <c r="B113" s="93" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>1122</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
+      <c r="B116" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="16" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="16"/>
-      <c r="B101" s="94" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="16"/>
-      <c r="B102" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="16"/>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104">
-        <v>1</v>
-      </c>
-      <c r="B104" s="93" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105">
-        <v>1</v>
-      </c>
-      <c r="B105" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107">
-        <v>2</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108">
-        <v>3</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="16" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="16"/>
-      <c r="B111" s="16" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F111" s="16" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="16"/>
-      <c r="C112" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="16"/>
-      <c r="C113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G113" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="16"/>
-      <c r="C114" t="s">
-        <v>1227</v>
-      </c>
-      <c r="G114" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="16"/>
-      <c r="C115" t="s">
-        <v>1230</v>
-      </c>
-      <c r="G115" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="16"/>
-      <c r="C116" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="16"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="16"/>
-      <c r="C118" t="s">
-        <v>1229</v>
+      <c r="B117" t="s">
+        <v>1212</v>
       </c>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="16"/>
+      <c r="A119" s="16" t="s">
+        <v>1251</v>
+      </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="16"/>
+      <c r="B120" s="16" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F120" s="16" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="16" t="s">
-        <v>1233</v>
+      <c r="A121" s="16"/>
+      <c r="C121" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1253</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="16"/>
+      <c r="C122" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="123" spans="1:7">
-      <c r="B123" t="s">
+      <c r="A123" s="16"/>
+      <c r="C123" t="s">
         <v>1220</v>
       </c>
+      <c r="G123" t="s">
+        <v>1255</v>
+      </c>
     </row>
     <row r="124" spans="1:7">
-      <c r="B124" t="s">
-        <v>1221</v>
+      <c r="A124" s="16"/>
+      <c r="C124" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1256</v>
       </c>
     </row>
     <row r="125" spans="1:7">
-      <c r="B125" t="s">
+      <c r="A125" s="16"/>
+      <c r="C125" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="16"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="16"/>
+      <c r="C127" t="s">
         <v>1222</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
-      <c r="B126" t="s">
-        <v>1223</v>
-      </c>
-    </row>
     <row r="128" spans="1:7">
-      <c r="B128" t="s">
+      <c r="A128" s="16"/>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="16"/>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="16" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="16"/>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="B132" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="B133" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="B134" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="B135" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="B137" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="C138" s="22" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="16" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="B141" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="B142" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="B143" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="B144" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
+      <c r="B145" t="s">
         <v>1234</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
-      <c r="C129" s="22" t="s">
+    <row r="147" spans="2:7">
+      <c r="B147" t="s">
         <v>1235</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="16" t="s">
+    <row r="149" spans="2:7">
+      <c r="B149" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
-      <c r="B132" t="s">
+    <row r="150" spans="2:7">
+      <c r="C150" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="B133" t="s">
+      <c r="G150" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7">
+      <c r="C151" t="s">
         <v>1238</v>
       </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="B134" t="s">
+      <c r="G151" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7">
+      <c r="C152" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="B135" t="s">
+      <c r="G152" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7">
+      <c r="B156" s="22" t="s">
         <v>1240</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
-      <c r="B136" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="B138" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="B140" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="C141" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G141" t="s">
+    <row r="158" spans="2:7">
+      <c r="B158" s="16" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7">
+      <c r="C159" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7">
+      <c r="C160" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3">
+      <c r="C161" s="22" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
-      <c r="C142" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G142" t="s">
+    <row r="163" spans="3:3">
+      <c r="C163" t="s">
         <v>1249</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="C143" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G143" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="145" spans="2:3">
-      <c r="B145" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="147" spans="2:3">
-      <c r="B147" s="22" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="149" spans="2:3">
-      <c r="B149" s="16" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="150" spans="2:3">
-      <c r="C150" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="151" spans="2:3">
-      <c r="C151" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="152" spans="2:3">
-      <c r="C152" s="22" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="154" spans="2:3">
-      <c r="C154" t="s">
-        <v>1256</v>
       </c>
     </row>
   </sheetData>

--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="1579">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7414,18 +7414,38 @@
       </rPr>
       <t>, хляб</t>
     </r>
+  </si>
+  <si>
+    <t>Надежда</t>
+  </si>
+  <si>
+    <t>Локо</t>
+  </si>
+  <si>
+    <t>Тръгване</t>
+  </si>
+  <si>
+    <t>Ради</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7870,7 +7890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7887,93 +7907,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -7988,19 +8008,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14598,12 +14619,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="100">
         <f ca="1">TODAY()-F32</f>
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="99" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 3 дни</v>
+        <v>1 години, 9 месеца, 5 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -21540,7 +21561,7 @@
       <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="106" t="s">
         <v>1560</v>
       </c>
       <c r="C8" s="24"/>
@@ -21724,10 +21745,12 @@
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="2:8">
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="106" t="s">
         <v>1565</v>
       </c>
-      <c r="C24" s="24"/>
+      <c r="C24" s="106" t="s">
+        <v>1565</v>
+      </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
@@ -21735,10 +21758,12 @@
       <c r="H24" s="24"/>
     </row>
     <row r="25" spans="2:8">
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="106" t="s">
         <v>1566</v>
       </c>
-      <c r="C25" s="24"/>
+      <c r="C25" s="106" t="s">
+        <v>1566</v>
+      </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
@@ -21746,10 +21771,12 @@
       <c r="H25" s="24"/>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="106" t="s">
         <v>1567</v>
       </c>
-      <c r="C26" s="24"/>
+      <c r="C26" s="106" t="s">
+        <v>1567</v>
+      </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
@@ -21757,15 +21784,57 @@
       <c r="H26" s="24"/>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="106" t="s">
         <v>1568</v>
       </c>
-      <c r="C27" s="24"/>
+      <c r="C27" s="106" t="s">
+        <v>1568</v>
+      </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="C30" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D30">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="C31" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="C32" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D32">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D34">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="16" t="s">

--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="1579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1586">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7393,29 +7393,6 @@
     <t>Пазар:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>домати</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, хляб</t>
-    </r>
-  </si>
-  <si>
     <t>Надежда</t>
   </si>
   <si>
@@ -7426,26 +7403,42 @@
   </si>
   <si>
     <t>Ради</t>
+  </si>
+  <si>
+    <t>6 яйца + сирене + салата + десерт</t>
+  </si>
+  <si>
+    <t>кайсии</t>
+  </si>
+  <si>
+    <t>домати, хляб</t>
+  </si>
+  <si>
+    <t>организация за бокс</t>
+  </si>
+  <si>
+    <t>да не пия</t>
+  </si>
+  <si>
+    <t>да не пия 2-ро, 3-то кафе</t>
+  </si>
+  <si>
+    <t>да не пропускам тренировка по бокс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">да не </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7669,11 +7662,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -7890,7 +7882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7907,93 +7899,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -8008,20 +8000,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14619,12 +14614,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="100">
         <f ca="1">TODAY()-F32</f>
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="99" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 5 дни</v>
+        <v>1 години, 9 месеца, 15 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -21564,20 +21559,20 @@
       <c r="B8" s="106" t="s">
         <v>1560</v>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="106"/>
       <c r="D8" s="24" t="s">
         <v>1561</v>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="24" t="s">
-        <v>1560</v>
+      <c r="F8" s="49" t="s">
+        <v>1561</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
       <c r="D9" s="103"/>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -21585,10 +21580,10 @@
       <c r="H9" s="104"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="106" t="s">
         <v>1562</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="106" t="s">
         <v>1562</v>
       </c>
       <c r="D10" s="24" t="s">
@@ -21608,8 +21603,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="106"/>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
@@ -21617,25 +21612,23 @@
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="106" t="s">
         <v>1563</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="106" t="s">
         <v>1564</v>
       </c>
       <c r="D12" s="103"/>
       <c r="E12" s="24" t="s">
         <v>1563</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>1564</v>
-      </c>
+      <c r="F12" s="24"/>
       <c r="G12" s="24"/>
       <c r="H12" s="104"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="106"/>
       <c r="D13" s="24"/>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
@@ -21643,8 +21636,8 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
@@ -21652,30 +21645,34 @@
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="107" t="s">
         <v>1571</v>
       </c>
-      <c r="C15" s="24"/>
+      <c r="C15" s="106"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="F15" s="109" t="s">
+        <v>1571</v>
+      </c>
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="106" t="s">
         <v>1572</v>
       </c>
-      <c r="C16" s="24"/>
+      <c r="C16" s="106"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="F16" s="24" t="s">
+        <v>1579</v>
+      </c>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
+      <c r="B17" s="106"/>
+      <c r="C17" s="106"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -21683,10 +21680,10 @@
       <c r="H17" s="24"/>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="107" t="s">
         <v>1573</v>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="106"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -21694,10 +21691,10 @@
       <c r="H18" s="24"/>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="105" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C19" s="24"/>
+      <c r="B19" s="106" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C19" s="106"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -21705,8 +21702,8 @@
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="106"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
@@ -21714,30 +21711,34 @@
       <c r="H20" s="24"/>
     </row>
     <row r="21" spans="2:8">
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="107" t="s">
         <v>1569</v>
       </c>
-      <c r="C21" s="24"/>
+      <c r="C21" s="106"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="F21" s="109" t="s">
+        <v>1569</v>
+      </c>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
     </row>
     <row r="22" spans="2:8">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="106" t="s">
         <v>1570</v>
       </c>
-      <c r="C22" s="24"/>
+      <c r="C22" s="106"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="F22" s="24" t="s">
+        <v>1578</v>
+      </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
     </row>
     <row r="23" spans="2:8">
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
@@ -21753,7 +21754,9 @@
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="F24" s="108" t="s">
+        <v>1565</v>
+      </c>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
     </row>
@@ -21766,74 +21769,105 @@
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="F25" s="105" t="s">
+        <v>1566</v>
+      </c>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="106" t="s">
+      <c r="B26" s="105" t="s">
         <v>1567</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="105" t="s">
         <v>1567</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="F26" s="106" t="s">
+        <v>1567</v>
+      </c>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="105" t="s">
         <v>1568</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="105" t="s">
         <v>1568</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
+      <c r="F27" s="106" t="s">
+        <v>1568</v>
+      </c>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
     </row>
-    <row r="30" spans="2:8">
-      <c r="C30" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D30">
+    <row r="33" spans="2:3">
+      <c r="B33" s="16" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C34">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="C31" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="C32" t="s">
-        <v>1577</v>
-      </c>
-      <c r="D32">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33" t="s">
+    <row r="35" spans="2:3">
+      <c r="B35" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C35">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C36">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C37">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" t="s">
         <v>1575</v>
       </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4">
-      <c r="C34" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D34">
+      <c r="C38">
         <v>5.25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45" t="s">
+        <v>1585</v>
       </c>
     </row>
     <row r="109" spans="1:2">

--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1593">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7363,9 +7363,6 @@
     <t>под.готв</t>
   </si>
   <si>
-    <t>готвене</t>
-  </si>
-  <si>
     <t>без алкохол</t>
   </si>
   <si>
@@ -7381,39 +7378,12 @@
     <t>Вечеря:</t>
   </si>
   <si>
-    <t>2 пържоли + картофена салата</t>
-  </si>
-  <si>
     <t>Следобедна:</t>
   </si>
   <si>
-    <t>2 банана + орехи</t>
-  </si>
-  <si>
     <t>Пазар:</t>
   </si>
   <si>
-    <t>Надежда</t>
-  </si>
-  <si>
-    <t>Локо</t>
-  </si>
-  <si>
-    <t>Тръгване</t>
-  </si>
-  <si>
-    <t>Ради</t>
-  </si>
-  <si>
-    <t>6 яйца + сирене + салата + десерт</t>
-  </si>
-  <si>
-    <t>кайсии</t>
-  </si>
-  <si>
-    <t>домати, хляб</t>
-  </si>
-  <si>
     <t>организация за бокс</t>
   </si>
   <si>
@@ -7427,18 +7397,77 @@
   </si>
   <si>
     <t xml:space="preserve">да не </t>
+  </si>
+  <si>
+    <t>2 сливи</t>
+  </si>
+  <si>
+    <t>Пазар: картофи</t>
+  </si>
+  <si>
+    <t>Готв: картофена салата</t>
+  </si>
+  <si>
+    <t>Вечеря: 2 пържоли + картофена салата</t>
+  </si>
+  <si>
+    <t>Книга: 20 мин</t>
+  </si>
+  <si>
+    <t>Обяд: сарми</t>
+  </si>
+  <si>
+    <t>Как да стана 2-пъти по ценен</t>
+  </si>
+  <si>
+    <t>Кафе</t>
+  </si>
+  <si>
+    <t>Организация за пазар</t>
+  </si>
+  <si>
+    <t>кромид лук</t>
+  </si>
+  <si>
+    <t>боборинки</t>
+  </si>
+  <si>
+    <t>краставици</t>
+  </si>
+  <si>
+    <t>картофена салата</t>
+  </si>
+  <si>
+    <t>2 пържоли</t>
+  </si>
+  <si>
+    <t>таратор</t>
+  </si>
+  <si>
+    <t>Готвене:</t>
+  </si>
+  <si>
+    <t>1 сливи</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7882,7 +7911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7899,93 +7928,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -8000,23 +8029,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14614,12 +14658,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="100">
         <f ca="1">TODAY()-F32</f>
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="99" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 15 дни</v>
+        <v>1 години, 9 месеца, 18 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -21482,7 +21526,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:S160"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.21875" customWidth="1"/>
@@ -21490,13 +21534,13 @@
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="16"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="16"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="B3" s="52" t="s">
         <v>1553</v>
       </c>
@@ -21519,16 +21563,27 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-    </row>
-    <row r="5" spans="1:8">
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>590</v>
+      </c>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="J4" s="113" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>7</v>
+      </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
@@ -21537,8 +21592,13 @@
       <c r="G5" s="24"/>
       <c r="H5" s="24"/>
     </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="24"/>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" s="106" t="s">
+        <v>1580</v>
+      </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -21546,7 +21606,10 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>9</v>
+      </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -21555,54 +21618,57 @@
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="106" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C8" s="106"/>
-      <c r="D8" s="24" t="s">
-        <v>1561</v>
-      </c>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="49" t="s">
-        <v>1561</v>
-      </c>
+      <c r="F8" s="24"/>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="J8" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>11</v>
+      </c>
       <c r="B9" s="106"/>
       <c r="C9" s="106"/>
-      <c r="D9" s="103"/>
+      <c r="D9" s="49"/>
       <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="49"/>
       <c r="G9" s="24"/>
-      <c r="H9" s="104"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="24"/>
+      <c r="J9" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>12</v>
+      </c>
       <c r="B10" s="106" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C10" s="106"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="104"/>
+      <c r="J10" t="s">
         <v>1562</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>1562</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>1562</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>1562</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>13</v>
+      </c>
       <c r="B11" s="106"/>
       <c r="C11" s="106"/>
       <c r="D11" s="24"/>
@@ -21610,32 +21676,46 @@
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="106" t="s">
+      <c r="J11" t="s">
         <v>1563</v>
       </c>
-      <c r="C12" s="106" t="s">
-        <v>1564</v>
-      </c>
-      <c r="D12" s="103"/>
-      <c r="E12" s="24" t="s">
-        <v>1563</v>
-      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>14</v>
+      </c>
+      <c r="B12" s="106"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
-      <c r="H12" s="104"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="106"/>
+      <c r="H12" s="24"/>
+      <c r="J12" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>15</v>
+      </c>
+      <c r="B13" s="106" t="s">
+        <v>1576</v>
+      </c>
       <c r="C13" s="106"/>
-      <c r="D13" s="24"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="H13" s="104"/>
+      <c r="J13" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>16</v>
+      </c>
       <c r="B14" s="106"/>
       <c r="C14" s="106"/>
       <c r="D14" s="24"/>
@@ -21643,57 +21723,81 @@
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="107" t="s">
-        <v>1571</v>
+      <c r="J14" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>17</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>1577</v>
       </c>
       <c r="C15" s="106"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
-      <c r="F15" s="109" t="s">
-        <v>1571</v>
-      </c>
+      <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="106" t="s">
-        <v>1572</v>
+      <c r="J15" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>18</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>1578</v>
       </c>
       <c r="C16" s="106"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="24" t="s">
-        <v>1579</v>
-      </c>
+      <c r="F16" s="109"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="106"/>
+      <c r="J16" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17">
+        <v>19</v>
+      </c>
+      <c r="B17" s="108" t="s">
+        <v>1579</v>
+      </c>
       <c r="C17" s="106"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="107" t="s">
-        <v>1573</v>
-      </c>
+      <c r="J17" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18">
+        <v>20</v>
+      </c>
+      <c r="B18" s="106"/>
       <c r="C18" s="106"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="106" t="s">
-        <v>1580</v>
-      </c>
+      <c r="J18" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19">
+        <v>21</v>
+      </c>
+      <c r="B19" s="107"/>
       <c r="C19" s="106"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
@@ -21701,7 +21805,10 @@
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="1:19">
+      <c r="A20">
+        <v>22</v>
+      </c>
       <c r="B20" s="106"/>
       <c r="C20" s="106"/>
       <c r="D20" s="24"/>
@@ -21709,432 +21816,510 @@
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="107" t="s">
-        <v>1569</v>
-      </c>
+      <c r="J20" s="16" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21">
+        <v>23</v>
+      </c>
+      <c r="B21" s="106"/>
       <c r="C21" s="106"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
-      <c r="F21" s="109" t="s">
-        <v>1569</v>
-      </c>
+      <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="106" t="s">
-        <v>1570</v>
-      </c>
+    <row r="22" spans="1:19">
+      <c r="A22">
+        <v>24</v>
+      </c>
+      <c r="B22" s="107"/>
       <c r="C22" s="106"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="24" t="s">
-        <v>1578</v>
-      </c>
+      <c r="F22" s="109"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="106"/>
+    <row r="23" spans="1:19">
+      <c r="B23" s="106" t="s">
+        <v>1564</v>
+      </c>
       <c r="C23" s="106"/>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="F23" s="108"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="1:19">
       <c r="B24" s="106" t="s">
         <v>1565</v>
       </c>
-      <c r="C24" s="106" t="s">
-        <v>1565</v>
-      </c>
+      <c r="C24" s="106"/>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
-      <c r="F24" s="108" t="s">
-        <v>1565</v>
-      </c>
+      <c r="F24" s="105"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="1:19">
       <c r="B25" s="106" t="s">
         <v>1566</v>
       </c>
-      <c r="C25" s="106" t="s">
-        <v>1566</v>
-      </c>
+      <c r="C25" s="105"/>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="105" t="s">
-        <v>1566</v>
-      </c>
+      <c r="F25" s="106"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="105" t="s">
+    <row r="26" spans="1:19">
+      <c r="B26" s="106" t="s">
         <v>1567</v>
       </c>
-      <c r="C26" s="105" t="s">
-        <v>1567</v>
-      </c>
+      <c r="C26" s="105"/>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="106" t="s">
-        <v>1567</v>
-      </c>
+      <c r="F26" s="106"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="105" t="s">
+    <row r="31" spans="1:19">
+      <c r="C31" s="114" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="86">
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" s="89">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>9</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>11</v>
+      </c>
+      <c r="G32" s="86">
+        <v>12</v>
+      </c>
+      <c r="H32">
+        <v>13</v>
+      </c>
+      <c r="I32">
+        <v>14</v>
+      </c>
+      <c r="J32">
+        <v>15</v>
+      </c>
+      <c r="K32">
+        <v>16</v>
+      </c>
+      <c r="L32">
+        <v>17</v>
+      </c>
+      <c r="M32">
+        <v>18</v>
+      </c>
+      <c r="N32">
+        <v>19</v>
+      </c>
+      <c r="O32">
+        <v>20</v>
+      </c>
+      <c r="P32">
+        <v>21</v>
+      </c>
+      <c r="Q32">
+        <v>22</v>
+      </c>
+      <c r="R32">
+        <v>23</v>
+      </c>
+      <c r="S32">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="117" t="s">
+        <v>590</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="116" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H33" s="118"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106" t="s">
+        <v>1592</v>
+      </c>
+      <c r="K33" s="106"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="112" t="s">
         <v>1568</v>
       </c>
-      <c r="C27" s="105" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="106" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="16" t="s">
-        <v>1581</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="B34" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C34">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C35">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="B36" t="s">
+      <c r="O33" s="106" t="s">
+        <v>134</v>
+      </c>
+      <c r="P33" s="107"/>
+      <c r="Q33" s="106"/>
+      <c r="R33" s="106"/>
+      <c r="S33" s="107"/>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="C34" s="115" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>1591</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="L35" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1588</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="L36" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1590</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="L37" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="L38" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="B39" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="B40" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="B41" t="s">
         <v>1574</v>
       </c>
-      <c r="C36">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C37">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="B38" t="s">
+    </row>
+    <row r="42" spans="1:19">
+      <c r="B42" t="s">
         <v>1575</v>
       </c>
-      <c r="C38">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3">
-      <c r="B42" t="s">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3">
-      <c r="B43" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="B44" t="s">
+    </row>
+    <row r="44" spans="1:19">
+      <c r="B44" s="16" t="s">
         <v>1584</v>
       </c>
     </row>
-    <row r="45" spans="2:3">
-      <c r="B45" t="s">
-        <v>1585</v>
+    <row r="106" spans="1:2">
+      <c r="A106" s="16" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="16"/>
+      <c r="B107" s="94" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="16"/>
+      <c r="B108" t="s">
+        <v>1208</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="16" t="s">
-        <v>1217</v>
-      </c>
+      <c r="A109" s="16"/>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="16"/>
-      <c r="B110" s="94" t="s">
-        <v>1221</v>
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110" s="93" t="s">
+        <v>1209</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="16"/>
+      <c r="A111">
+        <v>1</v>
+      </c>
       <c r="B111" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="16"/>
+        <v>1210</v>
+      </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>1</v>
-      </c>
-      <c r="B113" s="93" t="s">
-        <v>1209</v>
+        <v>2</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1211</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="116" spans="1:7">
-      <c r="A116">
-        <v>2</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1211</v>
+      <c r="A116" s="16" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="117" spans="1:7">
-      <c r="A117">
-        <v>3</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1212</v>
+      <c r="A117" s="16"/>
+      <c r="B117" s="16" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F117" s="16" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="16"/>
+      <c r="C118" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1253</v>
       </c>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="16" t="s">
-        <v>1251</v>
+      <c r="A119" s="16"/>
+      <c r="C119" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G119" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="16"/>
-      <c r="B120" s="16" t="s">
-        <v>1250</v>
-      </c>
-      <c r="F120" s="16" t="s">
-        <v>1252</v>
+      <c r="C120" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1255</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="16"/>
       <c r="C121" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="G121" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="16"/>
       <c r="C122" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="G122" t="s">
-        <v>1254</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="16"/>
-      <c r="C123" t="s">
-        <v>1220</v>
-      </c>
-      <c r="G123" t="s">
-        <v>1255</v>
-      </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="16"/>
       <c r="C124" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G124" t="s">
-        <v>1256</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="16"/>
-      <c r="C125" t="s">
-        <v>1224</v>
-      </c>
-      <c r="G125" t="s">
-        <v>1225</v>
-      </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="16"/>
     </row>
     <row r="127" spans="1:7">
-      <c r="A127" s="16"/>
-      <c r="C127" t="s">
-        <v>1222</v>
+      <c r="A127" s="16" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="16"/>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="16"/>
+      <c r="B129" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="16" t="s">
-        <v>1226</v>
+      <c r="B130" t="s">
+        <v>1214</v>
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="16"/>
+      <c r="B131" t="s">
+        <v>1215</v>
+      </c>
     </row>
     <row r="132" spans="1:3">
       <c r="B132" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="B133" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="B134" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="B135" t="s">
-        <v>1216</v>
+      <c r="C135" s="22" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="B137" t="s">
-        <v>1227</v>
+      <c r="A137" s="16" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="C138" s="22" t="s">
-        <v>1228</v>
+      <c r="B138" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="B139" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="16" t="s">
-        <v>1229</v>
+      <c r="B140" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="B141" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="B142" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="B143" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="B144" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="145" spans="2:7">
-      <c r="B145" t="s">
-        <v>1234</v>
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
+      <c r="B146" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="147" spans="2:7">
-      <c r="B147" t="s">
-        <v>1235</v>
+      <c r="C147" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
+      <c r="C148" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="149" spans="2:7">
-      <c r="B149" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="150" spans="2:7">
-      <c r="C150" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1241</v>
+      <c r="C149" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="151" spans="2:7">
-      <c r="C151" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7">
-      <c r="C152" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="154" spans="2:7">
-      <c r="B154" t="s">
+      <c r="B151" t="s">
         <v>1244</v>
       </c>
     </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="22" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7">
+      <c r="B155" s="16" t="s">
+        <v>1245</v>
+      </c>
+    </row>
     <row r="156" spans="2:7">
-      <c r="B156" s="22" t="s">
-        <v>1240</v>
+      <c r="C156" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="C157" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="158" spans="2:7">
-      <c r="B158" s="16" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="159" spans="2:7">
-      <c r="C159" t="s">
-        <v>1246</v>
+      <c r="C158" s="22" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="160" spans="2:7">
       <c r="C160" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="161" spans="3:3">
-      <c r="C161" s="22" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="163" spans="3:3">
-      <c r="C163" t="s">
         <v>1249</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="1644">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7384,9 +7384,6 @@
     <t>Пазар:</t>
   </si>
   <si>
-    <t>организация за бокс</t>
-  </si>
-  <si>
     <t>да не пия</t>
   </si>
   <si>
@@ -7408,9 +7405,6 @@
     <t>Готв: картофена салата</t>
   </si>
   <si>
-    <t>Вечеря: 2 пържоли + картофена салата</t>
-  </si>
-  <si>
     <t>Книга: 20 мин</t>
   </si>
   <si>
@@ -7423,24 +7417,6 @@
     <t>Кафе</t>
   </si>
   <si>
-    <t>Организация за пазар</t>
-  </si>
-  <si>
-    <t>кромид лук</t>
-  </si>
-  <si>
-    <t>боборинки</t>
-  </si>
-  <si>
-    <t>краставици</t>
-  </si>
-  <si>
-    <t>картофена салата</t>
-  </si>
-  <si>
-    <t>2 пържоли</t>
-  </si>
-  <si>
     <t>таратор</t>
   </si>
   <si>
@@ -7448,13 +7424,190 @@
   </si>
   <si>
     <t>1 сливи</t>
+  </si>
+  <si>
+    <t>организация за пазар</t>
+  </si>
+  <si>
+    <t>авокадо</t>
+  </si>
+  <si>
+    <t>набирания</t>
+  </si>
+  <si>
+    <t>планк</t>
+  </si>
+  <si>
+    <t>1 пържола</t>
+  </si>
+  <si>
+    <t>1 картоф</t>
+  </si>
+  <si>
+    <t>Книга: 10 мин</t>
+  </si>
+  <si>
+    <t>Мартин</t>
+  </si>
+  <si>
+    <t>Никилай</t>
+  </si>
+  <si>
+    <t>Мите</t>
+  </si>
+  <si>
+    <t>Пепи</t>
+  </si>
+  <si>
+    <t>Слави</t>
+  </si>
+  <si>
+    <t>Иван</t>
+  </si>
+  <si>
+    <t>Тодор</t>
+  </si>
+  <si>
+    <t>Коки</t>
+  </si>
+  <si>
+    <t>Веско</t>
+  </si>
+  <si>
+    <t>Влади</t>
+  </si>
+  <si>
+    <t>Вальо</t>
+  </si>
+  <si>
+    <t>Жаорката</t>
+  </si>
+  <si>
+    <t>Жоро</t>
+  </si>
+  <si>
+    <t>Ради</t>
+  </si>
+  <si>
+    <t>Мишо</t>
+  </si>
+  <si>
+    <t>Павел</t>
+  </si>
+  <si>
+    <t>Димо</t>
+  </si>
+  <si>
+    <t>Юли</t>
+  </si>
+  <si>
+    <t>Свилен</t>
+  </si>
+  <si>
+    <t>Ники</t>
+  </si>
+  <si>
+    <t>Котов</t>
+  </si>
+  <si>
+    <t>Лсико</t>
+  </si>
+  <si>
+    <t>Ванката</t>
+  </si>
+  <si>
+    <t>Митко</t>
+  </si>
+  <si>
+    <t>Чаво</t>
+  </si>
+  <si>
+    <t>Станислав</t>
+  </si>
+  <si>
+    <t>Стефан</t>
+  </si>
+  <si>
+    <t>Орлин</t>
+  </si>
+  <si>
+    <t>Краси</t>
+  </si>
+  <si>
+    <t>Евгени</t>
+  </si>
+  <si>
+    <t>Росен</t>
+  </si>
+  <si>
+    <t>ПешО</t>
+  </si>
+  <si>
+    <t>Найден</t>
+  </si>
+  <si>
+    <t>Илиян</t>
+  </si>
+  <si>
+    <t>Тошко</t>
+  </si>
+  <si>
+    <t>Кире</t>
+  </si>
+  <si>
+    <t>Шарано</t>
+  </si>
+  <si>
+    <t>Рускио</t>
+  </si>
+  <si>
+    <t>Боце</t>
+  </si>
+  <si>
+    <t>Васко</t>
+  </si>
+  <si>
+    <t>Иво</t>
+  </si>
+  <si>
+    <t>Милети</t>
+  </si>
+  <si>
+    <t>Кацката</t>
+  </si>
+  <si>
+    <t>Адриан</t>
+  </si>
+  <si>
+    <t>Сике</t>
+  </si>
+  <si>
+    <t>Светли</t>
+  </si>
+  <si>
+    <t>Емо</t>
+  </si>
+  <si>
+    <t>Владо</t>
+  </si>
+  <si>
+    <t>Айвазов</t>
+  </si>
+  <si>
+    <t>Адашо</t>
+  </si>
+  <si>
+    <t>Янков</t>
+  </si>
+  <si>
+    <t>Ников</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7697,6 +7850,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -7730,7 +7892,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -7907,11 +8069,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border diagonalUp="1">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8029,10 +8211,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -8045,22 +8226,24 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14526,16 +14709,16 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="96" t="s">
         <v>1462</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="96" t="s">
         <v>1463</v>
       </c>
-      <c r="F4" s="97" t="s">
+      <c r="F4" s="96" t="s">
         <v>1464</v>
       </c>
-      <c r="H4" s="97" t="s">
+      <c r="H4" s="96" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -14543,12 +14726,12 @@
       <c r="C6" s="24" t="s">
         <v>1460</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="96" t="s">
         <v>1461</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="D9" s="97" t="s">
+      <c r="D9" s="96" t="s">
         <v>1466</v>
       </c>
       <c r="F9" s="24" t="s">
@@ -14566,24 +14749,24 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="96" t="s">
         <v>1474</v>
       </c>
-      <c r="D18" s="97" t="s">
+      <c r="D18" s="96" t="s">
         <v>1475</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="101" t="s">
         <v>1552</v>
       </c>
-      <c r="H18" s="97" t="s">
+      <c r="H18" s="96" t="s">
         <v>1476</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="C21" s="97" t="s">
+      <c r="C21" s="96" t="s">
         <v>1472</v>
       </c>
-      <c r="G21" s="97" t="s">
+      <c r="G21" s="96" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -14624,17 +14807,17 @@
     </row>
     <row r="32" spans="1:10">
       <c r="B32" s="4"/>
-      <c r="C32" s="98">
+      <c r="C32" s="97">
         <v>16507</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="101">
+      <c r="F32" s="100">
         <v>45554</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="98">
+      <c r="I32" s="97">
         <v>45556</v>
       </c>
       <c r="J32" s="11"/>
@@ -14656,14 +14839,14 @@
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="4"/>
-      <c r="C36" s="100">
+      <c r="C36" s="99">
         <f ca="1">TODAY()-F32</f>
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E36" s="4"/>
-      <c r="F36" s="99" t="str">
+      <c r="F36" s="98" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 18 дни</v>
+        <v>1 години, 9 месеца, 21 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -14816,12 +14999,12 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="93" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="93" t="s">
         <v>1550</v>
       </c>
     </row>
@@ -16348,7 +16531,7 @@
       </c>
     </row>
     <row r="215" spans="1:11">
-      <c r="B215" s="95"/>
+      <c r="B215" s="94"/>
     </row>
     <row r="216" spans="1:11">
       <c r="B216" s="48" t="s">
@@ -18210,7 +18393,7 @@
       </c>
     </row>
     <row r="137" spans="2:5">
-      <c r="C137" s="96" t="s">
+      <c r="C137" s="95" t="s">
         <v>1398</v>
       </c>
     </row>
@@ -18424,7 +18607,7 @@
       </c>
     </row>
     <row r="186" spans="2:4">
-      <c r="C186" s="96" t="s">
+      <c r="C186" s="95" t="s">
         <v>1432</v>
       </c>
     </row>
@@ -21526,11 +21709,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S160"/>
+  <dimension ref="A1:S164"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21567,17 +21749,17 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="109" t="s">
         <v>590</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="J4" s="113" t="s">
-        <v>1582</v>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="J4" s="111" t="s">
+        <v>1580</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -21596,8 +21778,8 @@
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="B6" s="106" t="s">
-        <v>1580</v>
+      <c r="B6" s="24" t="s">
+        <v>1578</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -21637,8 +21819,8 @@
       <c r="A9">
         <v>11</v>
       </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="106"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
       <c r="D9" s="49"/>
       <c r="E9" s="24"/>
       <c r="F9" s="49"/>
@@ -21652,15 +21834,15 @@
       <c r="A10">
         <v>12</v>
       </c>
-      <c r="B10" s="106" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C10" s="106"/>
-      <c r="D10" s="103"/>
+      <c r="B10" s="105" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C10" s="105"/>
+      <c r="D10" s="102"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="104"/>
+      <c r="H10" s="103"/>
       <c r="J10" t="s">
         <v>1562</v>
       </c>
@@ -21669,8 +21851,8 @@
       <c r="A11">
         <v>13</v>
       </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
@@ -21684,8 +21866,8 @@
       <c r="A12">
         <v>14</v>
       </c>
-      <c r="B12" s="106"/>
-      <c r="C12" s="106"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
@@ -21699,15 +21881,15 @@
       <c r="A13">
         <v>15</v>
       </c>
-      <c r="B13" s="106" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C13" s="106"/>
-      <c r="D13" s="103"/>
+      <c r="B13" s="105" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C13" s="105"/>
+      <c r="D13" s="102"/>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="104"/>
+      <c r="H13" s="103"/>
       <c r="J13" t="s">
         <v>1570</v>
       </c>
@@ -21716,8 +21898,8 @@
       <c r="A14">
         <v>16</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="106"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
@@ -21731,10 +21913,12 @@
       <c r="A15">
         <v>17</v>
       </c>
-      <c r="B15" s="108" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C15" s="106"/>
+      <c r="B15" s="117" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>514</v>
+      </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
@@ -21748,13 +21932,13 @@
       <c r="A16">
         <v>18</v>
       </c>
-      <c r="B16" s="108" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C16" s="106"/>
+      <c r="B16" s="105" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C16" s="105"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="109"/>
+      <c r="F16" s="108"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="J16" t="s">
@@ -21765,12 +21949,16 @@
       <c r="A17">
         <v>19</v>
       </c>
-      <c r="B17" s="108" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C17" s="106"/>
+      <c r="B17" s="110" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C17" s="110" t="s">
+        <v>594</v>
+      </c>
       <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
+      <c r="E17" s="24" t="s">
+        <v>594</v>
+      </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
@@ -21782,8 +21970,8 @@
       <c r="A18">
         <v>20</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="106"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -21797,8 +21985,8 @@
       <c r="A19">
         <v>21</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="106"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -21809,95 +21997,135 @@
       <c r="A20">
         <v>22</v>
       </c>
-      <c r="B20" s="106"/>
-      <c r="C20" s="106"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="J20" s="16" t="s">
-        <v>1571</v>
+        <v>1585</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>1186</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21">
         <v>23</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
+      <c r="J21" t="s">
+        <v>1586</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1587</v>
+      </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22">
         <v>24</v>
       </c>
-      <c r="B22" s="107"/>
-      <c r="C22" s="106"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="109"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
+      <c r="J22" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1588</v>
+      </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="B23" s="106" t="s">
+      <c r="B23" s="104" t="s">
         <v>1564</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="108"/>
+      <c r="C23" s="118" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D23" s="118" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F23" s="107"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="B24" s="106" t="s">
+      <c r="B24" s="104" t="s">
         <v>1565</v>
       </c>
-      <c r="C24" s="106"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="105"/>
+      <c r="C24" s="104" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D24" s="104" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F24" s="104"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:19">
-      <c r="B25" s="106" t="s">
+      <c r="B25" s="104" t="s">
         <v>1566</v>
       </c>
-      <c r="C25" s="105"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="106"/>
+      <c r="C25" s="104" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D25" s="118" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F25" s="105"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
     </row>
     <row r="26" spans="1:19">
-      <c r="B26" s="106" t="s">
+      <c r="B26" s="118" t="s">
         <v>1567</v>
       </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="106"/>
+      <c r="C26" s="104" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D26" s="118" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F26" s="105"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="C31" s="114" t="s">
-        <v>1583</v>
+      <c r="B31" s="112"/>
+      <c r="C31" s="112" t="s">
+        <v>1581</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="86">
         <v>6</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="89">
         <v>7</v>
       </c>
       <c r="C32" s="89">
@@ -21953,45 +22181,46 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="117" t="s">
+      <c r="A33" s="115" t="s">
         <v>590</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="116"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="114"/>
       <c r="D33" s="34"/>
       <c r="E33" s="24"/>
       <c r="F33" s="65"/>
-      <c r="G33" s="116" t="s">
-        <v>1581</v>
-      </c>
-      <c r="H33" s="118"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106" t="s">
-        <v>1592</v>
-      </c>
-      <c r="K33" s="106"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="108"/>
-      <c r="N33" s="112" t="s">
+      <c r="G33" s="114" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H33" s="116"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="105" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K33" s="105"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="107"/>
+      <c r="N33" s="110" t="s">
         <v>1568</v>
       </c>
-      <c r="O33" s="106" t="s">
+      <c r="O33" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="P33" s="107"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="106"/>
-      <c r="S33" s="107"/>
+      <c r="P33" s="106"/>
+      <c r="Q33" s="105"/>
+      <c r="R33" s="105"/>
+      <c r="S33" s="106"/>
     </row>
     <row r="34" spans="1:19">
-      <c r="C34" s="115" t="s">
-        <v>1580</v>
+      <c r="B34" s="113"/>
+      <c r="C34" s="113" t="s">
+        <v>1591</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>1570</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="N34" s="16" t="s">
         <v>1589</v>
@@ -21999,321 +22228,604 @@
     </row>
     <row r="35" spans="1:19">
       <c r="L35" t="s">
-        <v>1354</v>
-      </c>
-      <c r="M35" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="N35" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="L36" t="s">
-        <v>1585</v>
-      </c>
-      <c r="M36" t="s">
-        <v>1590</v>
+        <v>1368</v>
       </c>
       <c r="N36" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
-      <c r="L37" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="L38" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="39" spans="1:19">
       <c r="B39" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="40" spans="1:19">
       <c r="B40" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="B41" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="42" spans="1:19">
       <c r="B42" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
-      <c r="B44" s="16" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="16" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="G47" s="119"/>
+      <c r="H47" s="121" t="s">
+        <v>1461</v>
+      </c>
+      <c r="I47" s="119"/>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="F48" s="120"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="119"/>
+    </row>
+    <row r="51" spans="2:16">
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="2:16">
+      <c r="I52" s="119"/>
+      <c r="J52" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K52" s="119"/>
+    </row>
+    <row r="53" spans="2:16">
+      <c r="H53" s="119"/>
+      <c r="I53" t="s">
+        <v>1624</v>
+      </c>
+      <c r="J53" s="119"/>
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="2:16">
+      <c r="G54" s="119"/>
+      <c r="H54" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I54" s="119"/>
+    </row>
+    <row r="55" spans="2:16">
+      <c r="F55" s="119"/>
+      <c r="G55" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H55" s="119"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="2:16">
+      <c r="E56" s="119"/>
+      <c r="F56" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G56" s="119"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+    </row>
+    <row r="57" spans="2:16">
+      <c r="D57" s="120"/>
+      <c r="E57" s="10" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F57" s="119"/>
+      <c r="I57" s="119"/>
+      <c r="J57" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K57" t="s">
+        <v>612</v>
+      </c>
+      <c r="L57" t="s">
+        <v>1592</v>
+      </c>
+      <c r="M57" t="s">
+        <v>1593</v>
+      </c>
+      <c r="N57" t="s">
+        <v>613</v>
+      </c>
+      <c r="O57" t="s">
+        <v>616</v>
+      </c>
+      <c r="P57" s="119"/>
+    </row>
+    <row r="58" spans="2:16">
+      <c r="H58" s="119"/>
+      <c r="I58" t="s">
+        <v>617</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1594</v>
+      </c>
+      <c r="K58" t="s">
+        <v>1595</v>
+      </c>
+      <c r="L58" t="s">
+        <v>1596</v>
+      </c>
+      <c r="M58" t="s">
+        <v>1597</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1598</v>
+      </c>
+      <c r="O58" s="119"/>
+    </row>
+    <row r="59" spans="2:16">
+      <c r="G59" s="119"/>
+      <c r="H59" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K59" t="s">
+        <v>1602</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1603</v>
+      </c>
+      <c r="M59" t="s">
+        <v>1604</v>
+      </c>
+      <c r="N59" s="119"/>
+    </row>
+    <row r="60" spans="2:16">
+      <c r="F60" s="119"/>
+      <c r="G60" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K60" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L60" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M60" s="119"/>
+    </row>
+    <row r="61" spans="2:16">
+      <c r="E61" s="119"/>
+      <c r="F61" t="s">
+        <v>599</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1612</v>
+      </c>
+      <c r="J61" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K61" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L61" s="119"/>
+    </row>
+    <row r="62" spans="2:16">
+      <c r="D62" s="119"/>
+      <c r="E62" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1600</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1616</v>
+      </c>
+      <c r="I62" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1617</v>
+      </c>
+      <c r="K62" s="119"/>
+    </row>
+    <row r="63" spans="2:16">
+      <c r="C63" s="119"/>
+      <c r="D63" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1623</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J63" s="119"/>
+    </row>
+    <row r="64" spans="2:16">
+      <c r="B64" s="119"/>
+      <c r="C64" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I64" s="119"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="119"/>
+      <c r="B65" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D65" t="s">
+        <v>747</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H65" s="119"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G66" s="119"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="10" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="119"/>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="16" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="16"/>
-      <c r="B107" s="94" t="s">
+    <row r="111" spans="1:2">
+      <c r="A111" s="16"/>
+      <c r="B111" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="16"/>
-      <c r="B108" t="s">
+    <row r="112" spans="1:2">
+      <c r="A112" s="16"/>
+      <c r="B112" t="s">
         <v>1208</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="16"/>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
-        <v>1</v>
-      </c>
-      <c r="B110" s="93" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
-        <v>1</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1210</v>
-      </c>
-    </row>
     <row r="113" spans="1:7">
-      <c r="A113">
-        <v>2</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1211</v>
-      </c>
+      <c r="A113" s="16"/>
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117">
+        <v>2</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118">
         <v>3</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B118" t="s">
         <v>1212</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="16" t="s">
+    <row r="120" spans="1:7">
+      <c r="A120" s="16" t="s">
         <v>1251</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="16"/>
-      <c r="B117" s="16" t="s">
-        <v>1250</v>
-      </c>
-      <c r="F117" s="16" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="16"/>
-      <c r="C118" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G118" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="16"/>
-      <c r="C119" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G119" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="16"/>
-      <c r="C120" t="s">
-        <v>1220</v>
-      </c>
-      <c r="G120" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="16"/>
-      <c r="C121" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G121" t="s">
-        <v>1256</v>
+      <c r="B121" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F121" s="16" t="s">
+        <v>1252</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="16"/>
       <c r="C122" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="G122" t="s">
-        <v>1225</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="16"/>
+      <c r="C123" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="16"/>
       <c r="C124" t="s">
-        <v>1222</v>
+        <v>1220</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1255</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="16"/>
+      <c r="C125" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="16"/>
+      <c r="C126" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1225</v>
+      </c>
     </row>
     <row r="127" spans="1:7">
-      <c r="A127" s="16" t="s">
-        <v>1226</v>
-      </c>
+      <c r="A127" s="16"/>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="16"/>
+      <c r="C128" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="B129" t="s">
+      <c r="A129" s="16"/>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="16"/>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="16" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="16"/>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="B133" t="s">
         <v>1213</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="B130" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="B131" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="B132" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="B134" t="s">
-        <v>1227</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="C135" s="22" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="16" t="s">
-        <v>1229</v>
+      <c r="B135" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="B136" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="B138" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="B139" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="B140" t="s">
-        <v>1232</v>
+      <c r="B139" s="22"/>
+      <c r="C139" s="22" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="B141" t="s">
-        <v>1233</v>
+      <c r="A141" s="16" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="B142" t="s">
-        <v>1234</v>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="B143" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="B144" t="s">
-        <v>1235</v>
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
+      <c r="B145" t="s">
+        <v>1233</v>
       </c>
     </row>
     <row r="146" spans="2:7">
       <c r="B146" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
+      <c r="B148" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
+      <c r="B150" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="147" spans="2:7">
-      <c r="C147" t="s">
+    <row r="151" spans="2:7">
+      <c r="C151" t="s">
         <v>1237</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G151" t="s">
         <v>1241</v>
       </c>
     </row>
-    <row r="148" spans="2:7">
-      <c r="C148" t="s">
+    <row r="152" spans="2:7">
+      <c r="C152" t="s">
         <v>1238</v>
       </c>
-      <c r="G148" t="s">
+      <c r="G152" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="149" spans="2:7">
-      <c r="C149" t="s">
+    <row r="153" spans="2:7">
+      <c r="C153" t="s">
         <v>1239</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G153" t="s">
         <v>1243</v>
       </c>
     </row>
-    <row r="151" spans="2:7">
-      <c r="B151" t="s">
+    <row r="155" spans="2:7">
+      <c r="B155" t="s">
         <v>1244</v>
       </c>
     </row>
-    <row r="153" spans="2:7">
-      <c r="B153" s="22" t="s">
+    <row r="157" spans="2:7">
+      <c r="B157" t="s">
         <v>1240</v>
       </c>
     </row>
-    <row r="155" spans="2:7">
-      <c r="B155" s="16" t="s">
+    <row r="159" spans="2:7">
+      <c r="B159" t="s">
         <v>1245</v>
-      </c>
-    </row>
-    <row r="156" spans="2:7">
-      <c r="C156" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="157" spans="2:7">
-      <c r="C157" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="158" spans="2:7">
-      <c r="C158" s="22" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="160" spans="2:7">
       <c r="C160" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3">
+      <c r="C161" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3">
+      <c r="B162" s="22"/>
+      <c r="C162" s="22" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3">
+      <c r="C164" t="s">
         <v>1249</v>
       </c>
     </row>

--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1646">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7601,18 +7601,32 @@
   </si>
   <si>
     <t>Ников</t>
+  </si>
+  <si>
+    <t>Лостове</t>
+  </si>
+  <si>
+    <t>Добра вечеря</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8093,7 +8107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8110,93 +8124,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -8211,39 +8225,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14841,12 +14861,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="99">
         <f ca="1">TODAY()-F32</f>
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="98" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 21 дни</v>
+        <v>1 години, 9 месеца, 22 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -21755,7 +21775,9 @@
       <c r="C4" s="109"/>
       <c r="D4" s="109"/>
       <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
+      <c r="F4" s="123" t="s">
+        <v>590</v>
+      </c>
       <c r="G4" s="109"/>
       <c r="H4" s="109"/>
       <c r="J4" s="111" t="s">
@@ -21840,7 +21862,9 @@
       <c r="C10" s="105"/>
       <c r="D10" s="102"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="F10" s="122" t="s">
+        <v>591</v>
+      </c>
       <c r="G10" s="24"/>
       <c r="H10" s="103"/>
       <c r="J10" t="s">
@@ -21887,7 +21911,9 @@
       <c r="C13" s="105"/>
       <c r="D13" s="102"/>
       <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="F13" s="24" t="s">
+        <v>1341</v>
+      </c>
       <c r="G13" s="24"/>
       <c r="H13" s="103"/>
       <c r="J13" t="s">
@@ -21959,7 +21985,9 @@
       <c r="E17" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="F17" s="24"/>
+      <c r="F17" s="49" t="s">
+        <v>1645</v>
+      </c>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="J17" t="s">
@@ -21989,7 +22017,9 @@
       <c r="C19" s="105"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="F19" s="49" t="s">
+        <v>1644</v>
+      </c>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
     </row>
@@ -22057,10 +22087,12 @@
       <c r="D23" s="118" t="s">
         <v>1564</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="104" t="s">
         <v>1564</v>
       </c>
-      <c r="F23" s="107"/>
+      <c r="F23" s="110" t="s">
+        <v>1564</v>
+      </c>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
     </row>
@@ -22074,10 +22106,12 @@
       <c r="D24" s="104" t="s">
         <v>1565</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="104" t="s">
         <v>1565</v>
       </c>
-      <c r="F24" s="104"/>
+      <c r="F24" s="105" t="s">
+        <v>1565</v>
+      </c>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
     </row>
@@ -22091,10 +22125,12 @@
       <c r="D25" s="118" t="s">
         <v>1566</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="104" t="s">
         <v>1566</v>
       </c>
-      <c r="F25" s="105"/>
+      <c r="F25" s="105" t="s">
+        <v>1566</v>
+      </c>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
     </row>
@@ -22108,10 +22144,12 @@
       <c r="D26" s="118" t="s">
         <v>1567</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="104" t="s">
         <v>1567</v>
       </c>
-      <c r="F26" s="105"/>
+      <c r="F26" s="105" t="s">
+        <v>1567</v>
+      </c>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
     </row>
